--- a/Result/checksun_type/風機維護.xlsx
+++ b/Result/checksun_type/風機維護.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>41.23</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>46.87</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>46.87</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>31333478.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>46398517.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>46398517.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>131458358.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>82367727.08</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>82367727.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-12563936.95104639</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>31333478</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>31333478.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>41.15</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>45.63</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>46.99</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>45.63</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>46.99</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>36693061.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>56607545.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>56607545.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>134181709.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>82624485.32</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>82624485.31999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9404152.255840585</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>36693061</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>36693061.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>40.98999999999999</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>45.99</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>47.13</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>47.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>52683153.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>89118941.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>89118941.40000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>138816628.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>83437284.84</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>83437284.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-5128552.57498084</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>52683153</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>52683153.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>41.09</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>46.37</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>47.28</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>47.28</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>45580107.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>111884228.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>111884228.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>138885693.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>83731647.22</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>83731647.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-550614.5817890316</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>45580107</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>45580107.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>41.45</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>46.82</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>47.42</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>47.42</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>65702790.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>146516831.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>146516831</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>138891629.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>86052402.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>86052402.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>6770002.28640601</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>65702790</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>65702790.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>42.15</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>47.27</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>47.55</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>47.55</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>82378616.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>216518198.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>216518198.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>143652333.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>85485799.7</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>85485799.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>14830238.83788446</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>82378616</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>82378616.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>43.67</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>47.72</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>47.67</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>47.67</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>199250041.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>211755874.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>211755874.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>140443251.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>84907732.44</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>84907732.44</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>24028515.4529292</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>199250041</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>199250041.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>45.36</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>48.22</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>47.82</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>47.82</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>166509589.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>188514316.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>188514316.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>128881598.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>82208595.36</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>82208595.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>23788810.95824565</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>166509589</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>166509589.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>46.89</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>48.6</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>47.92</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>218743119.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>165887158.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>165887158.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>115754398.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>79329370.94</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>79329370.94</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>26104681.14590324</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>218743119</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>218743119.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>48.22000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>48.9</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>415709627.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>131266427.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>131266427.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>98323015.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>75737222.34</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>75737222.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>22884307.44448899</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>415709627</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>415709627.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>49.17999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>48.04</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>48.04</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>58566995.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>70786468.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>70786468.40000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>61990972.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>67919282.7</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>67919282.7</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-3637077.537691697</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>58566995</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>58566995.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>39.01000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>48.62</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>54.24</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>54.24</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>83358150.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>103153046.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>103153046</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-3680363.644825548</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>83358150</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>83358150.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>38.81</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>49.61</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>54.55</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>54.55</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>70285205.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>116746722.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>116746722.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-252677.836492613</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>70285205</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>70285205.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>50.62</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>54.92</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>54.92</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>82791269.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>201446352.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>201446352.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>6053713.06242919</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>82791269</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>82791269.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>39.73</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>51.71</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>55.28</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>55.28</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>154811716.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>200122209.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>200122209.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>13506703.45151642</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>154811716</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>154811716.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>40.59</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>52.74</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>55.61</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>52.74</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>55.61</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>124518890.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>178692409.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>178692409.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>15954973.84837258</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>124518890</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>124518890.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>42.70999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>53.86</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>55.96</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>55.96</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>151326532.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>0</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>22128342.42072523</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>151326532</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>151326532.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>44.64</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>54.97</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>56.3</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>56.3</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>493783356.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>0</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>27284895.0804888</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>493783356</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>493783356.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>46.5</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>55.96</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>56.57</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>56.57</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>76170552.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>0</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-3014864.229866385</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>76170552</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>76170552.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>49.34</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>57.02</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>56.89</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>56.89</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>47662718.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>0</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-1448331.950735688</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>47662718</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>47662718.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>51.77999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>57.86</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>57.86</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>57.1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>0</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>6046878.730569392</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>0</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>53.46</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>58.38</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>57.23</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>57.23</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>173211166.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>113037476.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>113037476.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>103615588.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>97097036.24</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>97097036.23999999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>6046878.730569392</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>173211166</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>173211166.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>31.12</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>33.95</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>33.95</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>17391925.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>24945827.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>24945827.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-5187307.558847457</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>17391925</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>17391925.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>25.66</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>31.63</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>34.09</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>34.09</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>14123190.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>34052459.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>34052459.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-3643777.178724259</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>14123190</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>14123190.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>25.69</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>32.18</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>34.27</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>34.27</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>16265843.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>80665488.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>80665488.59999999</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-958377.2721652538</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>16265843</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>16265843.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>26.03</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>32.79</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>34.46</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>34.46</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>35607113.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>84219876.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>84219876.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>2682566.104067795</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>35607113</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>35607113.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>26.98</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>33.41</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>34.66</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>34.66</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>41341066.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>81947035.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>81947035.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>5715828.923541166</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>41341066</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>41341066.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>28.61</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>34.05</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>34.84</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>34.84</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>62925085.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>0</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>9230572.66837664</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>62925085</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>62925085.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>30.1</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>34.69</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>35.02</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>34.69</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>35.02</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>247188336.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>0</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>11609398.38712816</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>247188336</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>247188336.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>31.47</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>35.38</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>35.18</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>35.18</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>34037781.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>0</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-5149391.707052823</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>34037781</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>34037781.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>35.96</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>35.33</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>35.33</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>24242908.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>0</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-6069054.102059469</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>24242908</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>24242908.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>33.60000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>36.37</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>36.37</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>35.42</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>0</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-5918603.298963025</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>0</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>33.82</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>35.47</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>35.47</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>14998956.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>34520283.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>34520283.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>32085998.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>45710534.7</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>45710534.7</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-5918603.298963025</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>14998956</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>14998956.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/風機維護.xlsx
+++ b/Result/checksun_type/風機維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>754.379</t>
+          <t>495.163</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-64.70</t>
+          <t>-59.35</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.20</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>45.3</v>
+        <v>44.99</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.87</v>
+        <v>46.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-167.12</t>
+          <t>-170.91</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>46398517.8</v>
+        <v>37373891.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>131458358.1</t>
+          <t>91945361.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>82367727.08</v>
+        <v>81397712.23999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-85059840</t>
+          <t>-54571469</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1728395.380203726</t>
+          <t>-886469.1881221232</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-12563936.95104639</t>
+          <t>-15268224.31391429</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>894.804</t>
+          <t>754.379</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-64.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>45.63</v>
+        <v>45.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.99</v>
+        <v>46.87</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-32.08</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-161.74</t>
+          <t>-167.12</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>56607545.4</v>
+        <v>46398517.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>134181709.8</t>
+          <t>131458358.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>82624485.31999999</v>
+        <v>82367727.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-77574164</t>
+          <t>-85059840</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4327001.258612839</t>
+          <t>1728395.380203726</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9404152.255840585</t>
+          <t>-12563936.95104639</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1280.793</t>
+          <t>894.804</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-35.80</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>45.99</v>
+        <v>45.63</v>
       </c>
       <c r="AN4" t="n">
-        <v>47.13</v>
+        <v>46.99</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-60.10</t>
+          <t>-45.39</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-154.73</t>
+          <t>-161.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>89118941.40000001</v>
+        <v>56607545.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>138816628.8</t>
+          <t>134181709.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>83437284.84</v>
+        <v>82624485.31999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-49697687</t>
+          <t>-77574164</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6823574.624877097</t>
+          <t>4327001.258612839</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-5128552.57498084</t>
+          <t>-9404152.255840585</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1105.216</t>
+          <t>1280.793</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.44</t>
+          <t>-35.80</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>46.37</v>
+        <v>45.99</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.28</v>
+        <v>47.13</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-60.10</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-146.51</t>
+          <t>-154.73</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>111884228.6</v>
+        <v>89118941.40000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>138885693.6</t>
+          <t>138816628.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>83731647.22</v>
+        <v>83437284.84</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-27001465</t>
+          <t>-49697687</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>8996688.661214905</t>
+          <t>6823574.624877097</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-550614.5817890316</t>
+          <t>-5128552.57498084</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1580.018</t>
+          <t>1105.216</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>46.82</v>
+        <v>46.37</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.42</v>
+        <v>47.28</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-113.18</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-137.01</t>
+          <t>-146.51</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>146516831</v>
+        <v>111884228.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>138891629.3</t>
+          <t>138885693.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>86052402.7</v>
+        <v>83731647.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7625201</t>
+          <t>-27001465</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>10732561.97812471</t>
+          <t>8996688.661214905</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6770002.28640601</t>
+          <t>-550614.5817890316</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>47.27</v>
+        <v>46.82</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.55</v>
+        <v>47.42</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>216518198.4</v>
+        <v>146516831</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>85485799.7</v>
+        <v>86052402.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>14830238.83788446</t>
+          <t>6770002.28640601</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>47.72</v>
+        <v>47.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.67</v>
+        <v>47.55</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>211755874.2</v>
+        <v>216518198.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>84907732.44</v>
+        <v>85485799.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>24028515.4529292</t>
+          <t>14830238.83788446</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>48.22</v>
+        <v>47.72</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.82</v>
+        <v>47.67</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>188514316.2</v>
+        <v>211755874.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>82208595.36</v>
+        <v>84907732.44</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>23788810.95824565</t>
+          <t>24028515.4529292</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>48.6</v>
+        <v>48.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.92</v>
+        <v>47.82</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>165887158.6</v>
+        <v>188514316.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>79329370.94</v>
+        <v>82208595.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>26104681.14590324</t>
+          <t>23788810.95824565</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9151.696</t>
+          <t>5016.444</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>48</v>
+        <v>47.92</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-127.98</t>
+          <t>-524.68</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-94.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>131266427.6</v>
+        <v>165887158.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>98323015.2</t>
+          <t>115754398.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>75737222.34</v>
+        <v>79329370.94</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>32943412</t>
+          <t>50132760</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1931395.704591597</t>
+          <t>5650362.69556262</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>22884307.44448899</t>
+          <t>26104681.14590324</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1201.424</t>
+          <t>9151.696</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,54 +5314,54 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.17999999999999</t>
+          <t>48.22000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="AN12" t="n">
-        <v>48.04</v>
+        <v>48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,19 +5370,19 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-25.04</t>
+          <t>-127.98</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-84.07</t>
+          <t>-87.93</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>58566995.0</t>
+          <t>415709627.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>70786468.40000001</v>
+        <v>131266427.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>61990972.2</t>
+          <t>98323015.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>67919282.7</v>
+        <v>75737222.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8795496</t>
+          <t>32943412</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1878224.611753383</t>
+          <t>1931395.704591597</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3637077.537691697</t>
+          <t>22884307.44448899</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>58566995.0</t>
+          <t>415709627.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2106.06</t>
+          <t>1193.144</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.10</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-76.88</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>37.27</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-19.77</t>
+          <t>-17.28</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-10.35</t>
+          <t>-11.66</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.01000000000001</t>
+          <t>39.41</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>48.62</v>
+        <v>47.64</v>
       </c>
       <c r="AN13" t="n">
-        <v>54.24</v>
+        <v>53.93</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.61</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-18.89</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-144.82</t>
+          <t>-146.12</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>825504703.527977</t>
+          <t>824424892.6762178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>103153046</v>
+        <v>87822165.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133257287.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-45435122</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>5174529.578003587</t>
+          <t>3047715.886074118</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3680363.644825548</t>
+          <t>-8649759.419537961</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1860.309</t>
+          <t>2106.06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-77.97</t>
+          <t>-76.88</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>12.77</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>-19.77</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-10.35</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>39.01000000000001</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>49.61</v>
+        <v>48.62</v>
       </c>
       <c r="AN14" t="n">
-        <v>54.55</v>
+        <v>54.24</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>58.61</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-28.62</t>
+          <t>-18.89</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-142.70</t>
+          <t>-144.82</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,16 +6260,16 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>825504703.527977</t>
+          <t>824424892.6762178</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>70285205.0</t>
+          <t>83358150.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>116746722.4</v>
+        <v>103153046</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
@@ -6286,17 +6286,17 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>6784510.163972521</t>
+          <t>5174529.578003587</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-252677.836492613</t>
+          <t>-3680363.644825548</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>70285205.0</t>
+          <t>83358150.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-35.92</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
+          <t>40.35</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>38.5</t>
         </is>
       </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>37.15</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2129.764</t>
+          <t>1860.309</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-77.97</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-22.16</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>50.62</v>
+        <v>49.61</v>
       </c>
       <c r="AN15" t="n">
-        <v>54.92</v>
+        <v>54.55</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-36.90</t>
+          <t>-28.62</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-139.64</t>
+          <t>-142.70</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,16 +6690,16 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>825504703.527977</t>
+          <t>824424892.6762178</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>82791269.0</t>
+          <t>70285205.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>201446352.6</v>
+        <v>116746722.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
@@ -6716,17 +6716,17 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>8063998.891329818</t>
+          <t>6784510.163972521</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>6053713.06242919</t>
+          <t>-252677.836492613</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>82791269.0</t>
+          <t>70285205.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-36.58</t>
+          <t>-35.92</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3909.656</t>
+          <t>2129.764</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-77.19</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,17 +7034,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7054,53 +7054,53 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-22.16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>51.71</v>
+        <v>50.62</v>
       </c>
       <c r="AN16" t="n">
-        <v>55.28</v>
+        <v>54.92</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-45.17</t>
+          <t>-36.90</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-135.99</t>
+          <t>-139.64</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,16 +7120,16 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>825504703.527977</t>
+          <t>824424892.6762178</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>154811716.0</t>
+          <t>82791269.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>200122209.2</v>
+        <v>201446352.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
@@ -7146,17 +7146,17 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>8429505.405675387</t>
+          <t>8063998.891329818</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>13506703.45151642</t>
+          <t>6053713.06242919</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>154811716.0</t>
+          <t>82791269.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-33.67</t>
+          <t>-36.58</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,39 +7333,39 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3909.656</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>-2.37</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3220.761</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>38.4</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-2.84</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>0</t>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-77.99</t>
+          <t>-77.19</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-23.04</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>52.74</v>
+        <v>51.71</v>
       </c>
       <c r="AN17" t="n">
-        <v>55.61</v>
+        <v>55.28</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-58.77</t>
+          <t>-45.17</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-131.92</t>
+          <t>-135.99</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,16 +7550,16 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>825504703.527977</t>
+          <t>824424892.6762178</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>124518890.0</t>
+          <t>154811716.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>178692409.6</v>
+        <v>200122209.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
@@ -7576,17 +7576,17 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>7506378.488249744</t>
+          <t>8429505.405675387</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>15954973.84837258</t>
+          <t>13506703.45151642</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>124518890.0</t>
+          <t>154811716.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-33.67</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3762.915</t>
+          <t>3220.761</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-77.45</t>
+          <t>-77.99</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-20.71</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>42.70999999999999</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>53.86</v>
+        <v>52.74</v>
       </c>
       <c r="AN18" t="n">
-        <v>55.96</v>
+        <v>55.61</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>61.35</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-70.84</t>
+          <t>-58.77</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-127.23</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,16 +7980,16 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>825504703.527977</t>
+          <t>824424892.6762178</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>151326532.0</t>
+          <t>124518890.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>178692409.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
@@ -8006,17 +8006,17 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>5970270.240954683</t>
+          <t>7506378.488249744</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>22128342.42072523</t>
+          <t>15954973.84837258</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>151326532.0</t>
+          <t>124518890.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-34.42</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11938.065</t>
+          <t>3762.915</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-76.28</t>
+          <t>-77.45</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,17 +8324,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-20.71</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>42.70999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>54.97</v>
+        <v>53.86</v>
       </c>
       <c r="AN19" t="n">
-        <v>56.3</v>
+        <v>55.96</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.35</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-85.23</t>
+          <t>-70.84</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-122.41</t>
+          <t>-127.23</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>825504703.527977</t>
+          <t>824424892.6762178</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>493783356.0</t>
+          <t>151326532.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
@@ -8436,17 +8436,17 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>3032438.935541857</t>
+          <t>5970270.240954683</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>27284895.0804888</t>
+          <t>22128342.42072523</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>493783356.0</t>
+          <t>151326532.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-34.42</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1918.658</t>
+          <t>11938.065</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-77.25</t>
+          <t>-76.28</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-16.90</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-9.04</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>44.64</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>55.96</v>
+        <v>54.97</v>
       </c>
       <c r="AN20" t="n">
-        <v>56.57</v>
+        <v>56.3</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-107.56</t>
+          <t>-85.23</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-117.63</t>
+          <t>-122.41</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>825504703.527977</t>
+          <t>824424892.6762178</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>76170552.0</t>
+          <t>493783356.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
@@ -8866,17 +8866,17 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1377098.545357588</t>
+          <t>3032438.935541857</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3014864.229866385</t>
+          <t>27284895.0804888</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>76170552.0</t>
+          <t>493783356.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-33.83</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1080.792</t>
+          <t>1918.658</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-74.73</t>
+          <t>-77.25</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-13.47</t>
+          <t>-16.90</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>49.34</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>57.02</v>
+        <v>55.96</v>
       </c>
       <c r="AN21" t="n">
-        <v>56.89</v>
+        <v>56.57</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>62.94</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-117.71</t>
+          <t>-107.56</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-112.89</t>
+          <t>-117.63</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>825504703.527977</t>
+          <t>824424892.6762178</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>47662718.0</t>
+          <t>76170552.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
@@ -9296,17 +9296,17 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1079322.966355988</t>
+          <t>-1377098.545357588</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1448331.950735688</t>
+          <t>-3014864.229866385</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>47662718.0</t>
+          <t>76170552.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-26.50</t>
+          <t>-33.83</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1080.792</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-21.44</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-71.92</t>
+          <t>-74.73</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-10.52</t>
+          <t>-13.47</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>51.77999999999999</t>
+          <t>49.34</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>57.86</v>
+        <v>57.02</v>
       </c>
       <c r="AN22" t="n">
-        <v>57.1</v>
+        <v>56.89</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>63.46</t>
+          <t>62.94</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-133.71</t>
+          <t>-117.71</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-109.10</t>
+          <t>-112.89</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>825504703.527977</t>
+          <t>824424892.6762178</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47662718.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1012230.423741497</t>
+          <t>-1079322.966355988</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>6046878.730569392</t>
+          <t>-1448331.950735688</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47662718.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-18.33</t>
+          <t>-26.50</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3474.607</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-21.44</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-8.34</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-8.43</t>
+          <t>-10.52</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-10.48</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>53.46</t>
+          <t>51.77999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>58.38</v>
+        <v>57.86</v>
       </c>
       <c r="AN23" t="n">
-        <v>57.23</v>
+        <v>57.1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>63.93</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-185.30</t>
+          <t>-133.71</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.06</t>
+          <t>-109.10</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,33 +10130,33 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>825504703.527977</t>
+          <t>824424892.6762178</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>173211166.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>113037476.2</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>103615588.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>97097036.23999999</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>9421888</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-2295704.815434386</t>
+          <t>-1012230.423741497</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>173211166.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>649.691</t>
+          <t>612.432</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-60.87</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-44.67</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10474,73 +10474,73 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>70.27</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-14.68</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-9.4</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>31.12</v>
+        <v>30.62</v>
       </c>
       <c r="AN24" t="n">
-        <v>33.95</v>
+        <v>33.79</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-155.61</t>
+          <t>-157.54</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10560,20 +10560,20 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>234302822.4648997</t>
+          <t>234002523.4892704</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>24945827.4</v>
+        <v>19930126</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50938580.6</t>
         </is>
       </c>
       <c r="AZ24" t="n">
@@ -10581,22 +10581,22 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31008454</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-1011393.067796977</t>
+          <t>-1813147.762899367</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-5187307.558847457</t>
+          <t>-6222798.585962512</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-28.48</t>
+          <t>-29.54</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
@@ -10661,22 +10661,22 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10726,22 +10726,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>547.074</t>
+          <t>649.691</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-46.41</t>
+          <t>-44.67</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10904,73 +10904,73 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-18.87</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>25.66</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>31.63</v>
+        <v>31.12</v>
       </c>
       <c r="AN25" t="n">
-        <v>34.09</v>
+        <v>33.95</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>-32.22</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-152.71</t>
+          <t>-155.61</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10990,16 +10990,16 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>234302822.4648997</t>
+          <t>234002523.4892704</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>14123190.0</t>
+          <t>17391925.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>34052459.4</v>
+        <v>24945827.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
@@ -11016,17 +11016,17 @@
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-252135.8876059811</t>
+          <t>-1011393.067796977</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-3643777.178724259</t>
+          <t>-5187307.558847457</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>14123190.0</t>
+          <t>17391925.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-28.48</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
@@ -11101,12 +11101,12 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -11156,22 +11156,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>642.086</t>
+          <t>547.074</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-47.85</t>
+          <t>-46.41</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11313,17 +11313,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11334,63 +11334,63 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-20.16</t>
+          <t>-18.87</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>25.66</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>32.18</v>
+        <v>31.63</v>
       </c>
       <c r="AN26" t="n">
-        <v>34.27</v>
+        <v>34.09</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>-32.22</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-148.47</t>
+          <t>-152.71</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11420,16 +11420,16 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>234302822.4648997</t>
+          <t>234002523.4892704</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>16265843.0</t>
+          <t>14123190.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>80665488.59999999</v>
+        <v>34052459.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
@@ -11446,17 +11446,17 @@
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>364526.165324615</t>
+          <t>-252135.8876059811</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-958377.2721652538</t>
+          <t>-3643777.178724259</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>16265843.0</t>
+          <t>14123190.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-32.58</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="BM26" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN26" t="inlineStr">
@@ -11521,22 +11521,22 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1398.834</t>
+          <t>642.086</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11658,12 +11658,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-47.95</t>
+          <t>-47.85</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11764,73 +11764,73 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-20.62</t>
+          <t>-20.16</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>32.79</v>
+        <v>32.18</v>
       </c>
       <c r="AN27" t="n">
-        <v>34.46</v>
+        <v>34.27</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.77</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-55.82</t>
+          <t>-44.01</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-143.13</t>
+          <t>-148.47</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11850,16 +11850,16 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>234302822.4648997</t>
+          <t>234002523.4892704</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>35607113.0</t>
+          <t>16265843.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>84219876.2</v>
+        <v>80665488.59999999</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
@@ -11876,17 +11876,17 @@
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>605054.0630500456</t>
+          <t>364526.165324615</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>2682566.104067795</t>
+          <t>-958377.2721652538</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>35607113.0</t>
+          <t>16265843.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-32.72</t>
+          <t>-32.58</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="BM27" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN27" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -12016,22 +12016,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1600.961</t>
+          <t>1398.834</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-48.16</t>
+          <t>-47.95</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12194,73 +12194,73 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.62</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>33.41</v>
+        <v>32.79</v>
       </c>
       <c r="AN28" t="n">
-        <v>34.66</v>
+        <v>34.46</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-69.23</t>
+          <t>-55.82</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-143.13</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12280,16 +12280,16 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>234302822.4648997</t>
+          <t>234002523.4892704</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>41341066.0</t>
+          <t>35607113.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>81947035.2</v>
+        <v>84219876.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
@@ -12306,17 +12306,17 @@
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>227324.6010468184</t>
+          <t>605054.0630500456</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>5715828.923541166</t>
+          <t>2682566.104067795</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>41341066.0</t>
+          <t>35607113.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-32.72</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="BM28" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN28" t="inlineStr">
@@ -12381,22 +12381,22 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12446,22 +12446,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2373.75</t>
+          <t>1600.961</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-46.72</t>
+          <t>-48.16</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12603,17 +12603,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12624,12 +12624,12 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -12644,53 +12644,53 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>34.05</v>
+        <v>33.41</v>
       </c>
       <c r="AN29" t="n">
-        <v>34.84</v>
+        <v>34.66</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-82.56</t>
+          <t>-69.23</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-130.69</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12710,16 +12710,16 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>234302822.4648997</t>
+          <t>234002523.4892704</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>62925085.0</t>
+          <t>41341066.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>81947035.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
@@ -12736,17 +12736,17 @@
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-770585.2757703357</t>
+          <t>227324.6010468184</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>9230572.66837664</t>
+          <t>5715828.923541166</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>62925085.0</t>
+          <t>41341066.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-31.13</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="BM29" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN29" t="inlineStr">
@@ -12811,22 +12811,22 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9124.569</t>
+          <t>2373.75</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-46.11</t>
+          <t>-46.72</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13054,12 +13054,12 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -13074,53 +13074,53 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>28.61</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>34.69</v>
+        <v>34.05</v>
       </c>
       <c r="AN30" t="n">
-        <v>35.02</v>
+        <v>34.84</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-98.17</t>
+          <t>-82.56</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-124.36</t>
+          <t>-130.69</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13140,12 +13140,12 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>234302822.4648997</t>
+          <t>234002523.4892704</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>247188336.0</t>
+          <t>62925085.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
@@ -13166,17 +13166,17 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-2588977.629251604</t>
+          <t>-770585.2757703357</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>11609398.38712816</t>
+          <t>9230572.66837664</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>247188336.0</t>
+          <t>62925085.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-30.33</t>
+          <t>-31.13</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="BM30" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN30" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13311,17 +13311,17 @@
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13343,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-11.05</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1253.701</t>
+          <t>9124.569</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,12 +13378,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-44.36</t>
+          <t>-46.11</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13484,12 +13484,12 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -13499,58 +13499,58 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-13.73</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>35.38</v>
+        <v>34.69</v>
       </c>
       <c r="AN31" t="n">
-        <v>35.18</v>
+        <v>35.02</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-98.17</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-118.38</t>
+          <t>-124.36</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>234302822.4648997</t>
+          <t>234002523.4892704</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>34037781.0</t>
+          <t>247188336.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
@@ -13596,17 +13596,17 @@
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-5170500.541320652</t>
+          <t>-2588977.629251604</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-5149391.707052823</t>
+          <t>11609398.38712816</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>34037781.0</t>
+          <t>247188336.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-28.08</t>
+          <t>-30.33</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="BM31" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN31" t="inlineStr">
@@ -13671,22 +13671,22 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13736,22 +13736,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-11.05</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>804.084</t>
+          <t>1253.701</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-38.22</t>
+          <t>-44.36</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,12 +13893,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -13914,12 +13914,12 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -13929,58 +13929,58 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-13.73</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>35.96</v>
+        <v>35.38</v>
       </c>
       <c r="AN32" t="n">
-        <v>35.33</v>
+        <v>35.18</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-103.95</t>
+          <t>-108.86</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-113.38</t>
+          <t>-118.38</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>234302822.4648997</t>
+          <t>234002523.4892704</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>24242908.0</t>
+          <t>34037781.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
@@ -14026,17 +14026,17 @@
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-5174338.51118753</t>
+          <t>-5170500.541320652</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-6069054.102059469</t>
+          <t>-5149391.707052823</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>24242908.0</t>
+          <t>34037781.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-20.13</t>
+          <t>-28.08</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="BM32" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN32" t="inlineStr">
@@ -14106,17 +14106,17 @@
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -14166,22 +14166,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14218,7 +14218,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>804.084</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14238,12 +14238,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-23.89</t>
+          <t>-13.35</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-31.45</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,17 +14323,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14344,17 +14344,17 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -14364,53 +14364,53 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>33.60000000000001</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>36.37</v>
+        <v>35.96</v>
       </c>
       <c r="AN33" t="n">
-        <v>35.42</v>
+        <v>35.33</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-102.12</t>
+          <t>-103.95</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-109.90</t>
+          <t>-113.38</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>234302822.4648997</t>
+          <t>234002523.4892704</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24242908.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
@@ -14456,17 +14456,17 @@
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-5011662.949210814</t>
+          <t>-5174338.51118753</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-5918603.298963025</t>
+          <t>-6069054.102059469</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24242908.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-20.13</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="BM33" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN33" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>447.634</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-23.89</t>
+          <t>-25.75</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -14753,17 +14753,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14774,73 +14774,73 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-7.67</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-9.32</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>33.60000000000001</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>36.63</v>
+        <v>36.37</v>
       </c>
       <c r="AN34" t="n">
-        <v>35.47</v>
+        <v>35.42</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-150.41</t>
+          <t>-102.12</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-107.37</t>
+          <t>-109.90</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14860,33 +14860,33 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>234302822.4648997</t>
+          <t>234002523.4892704</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>14998956.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>34520283.8</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>32085998.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>45710534.7</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>2434285</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-4846764.703801322</t>
+          <t>-5011662.949210814</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>14998956.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14941,7 +14941,7 @@
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -15001,12 +15001,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -15026,17 +15026,17 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">

--- a/Result/checksun_type/風機維護.xlsx
+++ b/Result/checksun_type/風機維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>495.163</t>
+          <t>1130.918</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-59.35</t>
+          <t>-49.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>78.27</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.20</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>44.99</v>
+        <v>44.65</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.76</v>
+        <v>46.66</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-14.01</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-170.91</t>
+          <t>-173.49</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>37373891.4</v>
+        <v>37660141.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>91945361.2</t>
+          <t>74772185.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>81397712.23999999</v>
+        <v>81458753.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-54571469</t>
+          <t>-37112043</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-886469.1881221232</t>
+          <t>-3026572.764576255</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-15268224.31391429</t>
+          <t>-14797142.43507398</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>754.379</t>
+          <t>495.163</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-64.70</t>
+          <t>-59.35</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.20</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>45.3</v>
+        <v>44.99</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.87</v>
+        <v>46.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-167.12</t>
+          <t>-170.91</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>46398517.8</v>
+        <v>37373891.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>131458358.1</t>
+          <t>91945361.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>82367727.08</v>
+        <v>81397712.23999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-85059840</t>
+          <t>-54571469</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1728395.380203726</t>
+          <t>-886469.1881221232</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-12563936.95104639</t>
+          <t>-15268224.31391429</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>894.804</t>
+          <t>754.379</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-64.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>45.63</v>
+        <v>45.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.99</v>
+        <v>46.87</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-32.08</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-161.74</t>
+          <t>-167.12</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>56607545.4</v>
+        <v>46398517.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>134181709.8</t>
+          <t>131458358.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>82624485.31999999</v>
+        <v>82367727.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-77574164</t>
+          <t>-85059840</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>4327001.258612839</t>
+          <t>1728395.380203726</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9404152.255840585</t>
+          <t>-12563936.95104639</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1280.793</t>
+          <t>894.804</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-35.80</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>45.99</v>
+        <v>45.63</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.13</v>
+        <v>46.99</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-60.10</t>
+          <t>-45.39</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-154.73</t>
+          <t>-161.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>89118941.40000001</v>
+        <v>56607545.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>138816628.8</t>
+          <t>134181709.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>83437284.84</v>
+        <v>82624485.31999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-49697687</t>
+          <t>-77574164</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6823574.624877097</t>
+          <t>4327001.258612839</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-5128552.57498084</t>
+          <t>-9404152.255840585</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1105.216</t>
+          <t>1280.793</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.44</t>
+          <t>-35.80</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>46.37</v>
+        <v>45.99</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.28</v>
+        <v>47.13</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-60.10</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-146.51</t>
+          <t>-154.73</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>111884228.6</v>
+        <v>89118941.40000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>138885693.6</t>
+          <t>138816628.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>83731647.22</v>
+        <v>83437284.84</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-27001465</t>
+          <t>-49697687</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>8996688.661214905</t>
+          <t>6823574.624877097</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-550614.5817890316</t>
+          <t>-5128552.57498084</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1580.018</t>
+          <t>1105.216</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>46.82</v>
+        <v>46.37</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.42</v>
+        <v>47.28</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-113.18</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-137.01</t>
+          <t>-146.51</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>146516831</v>
+        <v>111884228.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>138891629.3</t>
+          <t>138885693.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>86052402.7</v>
+        <v>83731647.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7625201</t>
+          <t>-27001465</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>10732561.97812471</t>
+          <t>8996688.661214905</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>6770002.28640601</t>
+          <t>-550614.5817890316</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>47.27</v>
+        <v>46.82</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.55</v>
+        <v>47.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>216518198.4</v>
+        <v>146516831</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>85485799.7</v>
+        <v>86052402.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>14830238.83788446</t>
+          <t>6770002.28640601</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>47.72</v>
+        <v>47.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.67</v>
+        <v>47.55</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>211755874.2</v>
+        <v>216518198.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>84907732.44</v>
+        <v>85485799.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>24028515.4529292</t>
+          <t>14830238.83788446</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>48.22</v>
+        <v>47.72</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.82</v>
+        <v>47.67</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>188514316.2</v>
+        <v>211755874.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>82208595.36</v>
+        <v>84907732.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>23788810.95824565</t>
+          <t>24028515.4529292</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>48.6</v>
+        <v>48.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.92</v>
+        <v>47.82</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>165887158.6</v>
+        <v>188514316.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>79329370.94</v>
+        <v>82208595.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>26104681.14590324</t>
+          <t>23788810.95824565</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9151.696</t>
+          <t>5016.444</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>48</v>
+        <v>47.92</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-127.98</t>
+          <t>-524.68</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-94.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>131266427.6</v>
+        <v>165887158.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>98323015.2</t>
+          <t>115754398.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>75737222.34</v>
+        <v>79329370.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>32943412</t>
+          <t>50132760</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1931395.704591597</t>
+          <t>5650362.69556262</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>22884307.44448899</t>
+          <t>26104681.14590324</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1193.144</t>
+          <t>1488.337</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-34.10</t>
+          <t>-48.94</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>48.49</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-17.28</t>
+          <t>-15.58</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-11.66</t>
+          <t>-13.13</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.41</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>47.64</v>
+        <v>46.56</v>
       </c>
       <c r="AN13" t="n">
-        <v>53.93</v>
+        <v>53.6</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-146.12</t>
+          <t>-146.93</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>824424892.6762178</t>
+          <t>823371476.5879829</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>47864486.0</t>
+          <t>58724698.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>87822165.2</v>
+        <v>68604761.59999999</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>133257287.4</t>
+          <t>134363485.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-45435122</t>
+          <t>-65758723</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>3047715.886074118</t>
+          <t>871517.0457014539</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-8649759.419537961</t>
+          <t>-11097576.5763482</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>47864486.0</t>
+          <t>58724698.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2106.06</t>
+          <t>1193.144</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.10</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-76.88</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>37.27</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-19.77</t>
+          <t>-17.28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-10.35</t>
+          <t>-11.66</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.01000000000001</t>
+          <t>39.41</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>48.62</v>
+        <v>47.64</v>
       </c>
       <c r="AN14" t="n">
-        <v>54.24</v>
+        <v>53.93</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.61</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-18.89</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-144.82</t>
+          <t>-146.12</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,20 +6260,20 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>824424892.6762178</t>
+          <t>823371476.5879829</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>103153046</v>
+        <v>87822165.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133257287.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-45435122</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>5174529.578003587</t>
+          <t>3047715.886074118</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3680363.644825548</t>
+          <t>-8649759.419537961</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1860.309</t>
+          <t>2106.06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-77.97</t>
+          <t>-76.88</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>12.77</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>-19.77</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-10.35</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>39.01000000000001</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>49.61</v>
+        <v>48.62</v>
       </c>
       <c r="AN15" t="n">
-        <v>54.55</v>
+        <v>54.24</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>58.61</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-28.62</t>
+          <t>-18.89</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-142.70</t>
+          <t>-144.82</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,16 +6690,16 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>824424892.6762178</t>
+          <t>823371476.5879829</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>70285205.0</t>
+          <t>83358150.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>116746722.4</v>
+        <v>103153046</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
@@ -6716,17 +6716,17 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>6784510.163972521</t>
+          <t>5174529.578003587</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-252677.836492613</t>
+          <t>-3680363.644825548</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>70285205.0</t>
+          <t>83358150.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-35.92</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>40.35</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>38.5</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>37.15</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2129.764</t>
+          <t>1860.309</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-77.97</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-22.16</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>50.62</v>
+        <v>49.61</v>
       </c>
       <c r="AN16" t="n">
-        <v>54.92</v>
+        <v>54.55</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-36.90</t>
+          <t>-28.62</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-139.64</t>
+          <t>-142.70</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,16 +7120,16 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>824424892.6762178</t>
+          <t>823371476.5879829</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>82791269.0</t>
+          <t>70285205.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>201446352.6</v>
+        <v>116746722.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
@@ -7146,17 +7146,17 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>8063998.891329818</t>
+          <t>6784510.163972521</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6053713.06242919</t>
+          <t>-252677.836492613</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>82791269.0</t>
+          <t>70285205.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-36.58</t>
+          <t>-35.92</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3909.656</t>
+          <t>2129.764</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-77.19</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,17 +7464,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-22.16</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>51.71</v>
+        <v>50.62</v>
       </c>
       <c r="AN17" t="n">
-        <v>55.28</v>
+        <v>54.92</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-45.17</t>
+          <t>-36.90</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-135.99</t>
+          <t>-139.64</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,16 +7550,16 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>824424892.6762178</t>
+          <t>823371476.5879829</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>154811716.0</t>
+          <t>82791269.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>200122209.2</v>
+        <v>201446352.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
@@ -7576,17 +7576,17 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>8429505.405675387</t>
+          <t>8063998.891329818</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>13506703.45151642</t>
+          <t>6053713.06242919</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>154811716.0</t>
+          <t>82791269.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-33.67</t>
+          <t>-36.58</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3220.761</t>
+          <t>3909.656</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-77.99</t>
+          <t>-77.19</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-23.04</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>52.74</v>
+        <v>51.71</v>
       </c>
       <c r="AN18" t="n">
-        <v>55.61</v>
+        <v>55.28</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-58.77</t>
+          <t>-45.17</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-131.92</t>
+          <t>-135.99</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,16 +7980,16 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>824424892.6762178</t>
+          <t>823371476.5879829</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>124518890.0</t>
+          <t>154811716.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>178692409.6</v>
+        <v>200122209.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
@@ -8006,17 +8006,17 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>7506378.488249744</t>
+          <t>8429505.405675387</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>15954973.84837258</t>
+          <t>13506703.45151642</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>124518890.0</t>
+          <t>154811716.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-33.67</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3762.915</t>
+          <t>3220.761</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-77.45</t>
+          <t>-77.99</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-20.71</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>42.70999999999999</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>53.86</v>
+        <v>52.74</v>
       </c>
       <c r="AN19" t="n">
-        <v>55.96</v>
+        <v>55.61</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>61.35</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-70.84</t>
+          <t>-58.77</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-127.23</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,16 +8410,16 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>824424892.6762178</t>
+          <t>823371476.5879829</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>151326532.0</t>
+          <t>124518890.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>178692409.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
@@ -8436,17 +8436,17 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>5970270.240954683</t>
+          <t>7506378.488249744</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>22128342.42072523</t>
+          <t>15954973.84837258</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>151326532.0</t>
+          <t>124518890.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-34.42</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11938.065</t>
+          <t>3762.915</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-76.28</t>
+          <t>-77.45</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,17 +8754,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-20.71</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>42.70999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>54.97</v>
+        <v>53.86</v>
       </c>
       <c r="AN20" t="n">
-        <v>56.3</v>
+        <v>55.96</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.35</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-85.23</t>
+          <t>-70.84</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-122.41</t>
+          <t>-127.23</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>824424892.6762178</t>
+          <t>823371476.5879829</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>493783356.0</t>
+          <t>151326532.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
@@ -8866,17 +8866,17 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>3032438.935541857</t>
+          <t>5970270.240954683</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>27284895.0804888</t>
+          <t>22128342.42072523</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>493783356.0</t>
+          <t>151326532.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-34.42</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1918.658</t>
+          <t>11938.065</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-77.25</t>
+          <t>-76.28</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-16.90</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-9.04</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>44.64</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>55.96</v>
+        <v>54.97</v>
       </c>
       <c r="AN21" t="n">
-        <v>56.57</v>
+        <v>56.3</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-107.56</t>
+          <t>-85.23</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-117.63</t>
+          <t>-122.41</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>824424892.6762178</t>
+          <t>823371476.5879829</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>76170552.0</t>
+          <t>493783356.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
@@ -9296,17 +9296,17 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1377098.545357588</t>
+          <t>3032438.935541857</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3014864.229866385</t>
+          <t>27284895.0804888</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>76170552.0</t>
+          <t>493783356.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-33.83</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9441,17 +9441,17 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1080.792</t>
+          <t>1918.658</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-74.73</t>
+          <t>-77.25</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-13.47</t>
+          <t>-16.90</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>49.34</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>57.02</v>
+        <v>55.96</v>
       </c>
       <c r="AN22" t="n">
-        <v>56.89</v>
+        <v>56.57</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>62.94</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-117.71</t>
+          <t>-107.56</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-112.89</t>
+          <t>-117.63</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>824424892.6762178</t>
+          <t>823371476.5879829</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>47662718.0</t>
+          <t>76170552.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1079322.966355988</t>
+          <t>-1377098.545357588</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1448331.950735688</t>
+          <t>-3014864.229866385</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>47662718.0</t>
+          <t>76170552.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-26.50</t>
+          <t>-33.83</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1080.792</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-12.21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-71.92</t>
+          <t>-74.73</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-10.52</t>
+          <t>-13.47</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>51.77999999999999</t>
+          <t>49.34</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>57.86</v>
+        <v>57.02</v>
       </c>
       <c r="AN23" t="n">
-        <v>57.1</v>
+        <v>56.89</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>63.46</t>
+          <t>62.94</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-133.71</t>
+          <t>-117.71</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-109.10</t>
+          <t>-112.89</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>824424892.6762178</t>
+          <t>823371476.5879829</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47662718.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
@@ -10156,17 +10156,17 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1012230.423741497</t>
+          <t>-1079322.966355988</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>6046878.730569392</t>
+          <t>-1448331.950735688</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47662718.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-18.33</t>
+          <t>-26.50</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>612.432</t>
+          <t>465.71</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-60.87</t>
+          <t>-69.34</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-45.49</t>
+          <t>-46.52</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10474,73 +10474,73 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>70.27</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-14.68</t>
+          <t>-12.66</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>30.62</v>
+        <v>30.07</v>
       </c>
       <c r="AN24" t="n">
-        <v>33.79</v>
+        <v>33.64</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-157.54</t>
+          <t>-158.82</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10560,20 +10560,20 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>234002523.4892704</t>
+          <t>233694384.6492857</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>16262559.0</t>
+          <t>12203557.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>19930126</v>
+        <v>15249414.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>50938580.6</t>
+          <t>49734645.5</t>
         </is>
       </c>
       <c r="AZ24" t="n">
@@ -10581,22 +10581,22 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-31008454</t>
+          <t>-34485230</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-1813147.762899367</t>
+          <t>-2625970.797883155</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-6222798.585962512</t>
+          <t>-7096497.490293983</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>16262559.0</t>
+          <t>12203557.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-29.54</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10661,22 +10661,22 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10726,22 +10726,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>649.691</t>
+          <t>612.432</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-60.87</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-44.67</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10904,73 +10904,73 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>70.27</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-14.68</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-9.4</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>31.12</v>
+        <v>30.62</v>
       </c>
       <c r="AN25" t="n">
-        <v>33.95</v>
+        <v>33.79</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-155.61</t>
+          <t>-157.54</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10990,20 +10990,20 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>234002523.4892704</t>
+          <t>233694384.6492857</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>24945827.4</v>
+        <v>19930126</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50938580.6</t>
         </is>
       </c>
       <c r="AZ25" t="n">
@@ -11011,22 +11011,22 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31008454</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-1011393.067796977</t>
+          <t>-1813147.762899367</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-5187307.558847457</t>
+          <t>-6222798.585962512</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-28.48</t>
+          <t>-29.54</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11091,22 +11091,22 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -11131,47 +11131,47 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
+          <t>26.59</t>
+        </is>
+      </c>
+      <c r="BZ25" t="inlineStr">
+        <is>
+          <t>6427</t>
+        </is>
+      </c>
+      <c r="CA25" t="inlineStr">
+        <is>
+          <t>工程服務73.02%、系統及周邊產品20.33%、C零售及週邊產品5.91%、C產品零組件0.74% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>永崴投控-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC25" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD25" t="inlineStr">
+        <is>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="CE25" t="inlineStr">
+        <is>
+          <t>27.2</t>
+        </is>
+      </c>
+      <c r="CF25" t="inlineStr">
+        <is>
           <t>26.2</t>
         </is>
       </c>
-      <c r="BZ25" t="inlineStr">
-        <is>
-          <t>6550</t>
-        </is>
-      </c>
-      <c r="CA25" t="inlineStr">
-        <is>
-          <t>工程服務73.02%、系統及周邊產品20.33%、C零售及週邊產品5.91%、C產品零組件0.74% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>永崴投控-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CC25" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CD25" t="inlineStr">
-        <is>
-          <t>26.3</t>
-        </is>
-      </c>
-      <c r="CE25" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="CF25" t="inlineStr">
-        <is>
-          <t>26.3</t>
-        </is>
-      </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>547.074</t>
+          <t>649.691</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-46.41</t>
+          <t>-44.67</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11313,17 +11313,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11334,73 +11334,73 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-18.87</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>25.66</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>31.63</v>
+        <v>31.12</v>
       </c>
       <c r="AN26" t="n">
-        <v>34.09</v>
+        <v>33.95</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-32.22</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-152.71</t>
+          <t>-155.61</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11420,16 +11420,16 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>234002523.4892704</t>
+          <t>233694384.6492857</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>14123190.0</t>
+          <t>17391925.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>34052459.4</v>
+        <v>24945827.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
@@ -11446,17 +11446,17 @@
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-252135.8876059811</t>
+          <t>-1011393.067796977</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-3643777.178724259</t>
+          <t>-5187307.558847457</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>14123190.0</t>
+          <t>17391925.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-28.48</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>642.086</t>
+          <t>547.074</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11658,12 +11658,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-47.85</t>
+          <t>-46.41</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11764,63 +11764,63 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-20.16</t>
+          <t>-18.87</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>25.66</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>32.18</v>
+        <v>31.63</v>
       </c>
       <c r="AN27" t="n">
-        <v>34.27</v>
+        <v>34.09</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>-32.22</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-148.47</t>
+          <t>-152.71</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11850,16 +11850,16 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>234002523.4892704</t>
+          <t>233694384.6492857</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>16265843.0</t>
+          <t>14123190.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>80665488.59999999</v>
+        <v>34052459.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
@@ -11876,17 +11876,17 @@
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>364526.165324615</t>
+          <t>-252135.8876059811</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-958377.2721652538</t>
+          <t>-3643777.178724259</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>16265843.0</t>
+          <t>14123190.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-32.58</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11951,22 +11951,22 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -12016,22 +12016,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1398.834</t>
+          <t>642.086</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-47.95</t>
+          <t>-47.85</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12194,73 +12194,73 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-20.62</t>
+          <t>-20.16</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>32.79</v>
+        <v>32.18</v>
       </c>
       <c r="AN28" t="n">
-        <v>34.46</v>
+        <v>34.27</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.77</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-55.82</t>
+          <t>-44.01</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-143.13</t>
+          <t>-148.47</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12280,16 +12280,16 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>234002523.4892704</t>
+          <t>233694384.6492857</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>35607113.0</t>
+          <t>16265843.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>84219876.2</v>
+        <v>80665488.59999999</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
@@ -12306,17 +12306,17 @@
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>605054.0630500456</t>
+          <t>364526.165324615</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>2682566.104067795</t>
+          <t>-958377.2721652538</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>35607113.0</t>
+          <t>16265843.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-32.72</t>
+          <t>-32.58</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12446,22 +12446,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1600.961</t>
+          <t>1398.834</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-48.16</t>
+          <t>-47.95</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12603,17 +12603,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12624,73 +12624,73 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.62</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>33.41</v>
+        <v>32.79</v>
       </c>
       <c r="AN29" t="n">
-        <v>34.66</v>
+        <v>34.46</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-69.23</t>
+          <t>-55.82</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-143.13</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12710,16 +12710,16 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>234002523.4892704</t>
+          <t>233694384.6492857</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>41341066.0</t>
+          <t>35607113.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>81947035.2</v>
+        <v>84219876.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
@@ -12736,17 +12736,17 @@
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>227324.6010468184</t>
+          <t>605054.0630500456</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>5715828.923541166</t>
+          <t>2682566.104067795</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>41341066.0</t>
+          <t>35607113.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-32.72</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12811,22 +12811,22 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2373.75</t>
+          <t>1600.961</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-46.72</t>
+          <t>-48.16</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13054,12 +13054,12 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -13074,53 +13074,53 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>34.05</v>
+        <v>33.41</v>
       </c>
       <c r="AN30" t="n">
-        <v>34.84</v>
+        <v>34.66</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-82.56</t>
+          <t>-69.23</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-130.69</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13140,16 +13140,16 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>234002523.4892704</t>
+          <t>233694384.6492857</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>62925085.0</t>
+          <t>41341066.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>81947035.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
@@ -13166,17 +13166,17 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-770585.2757703357</t>
+          <t>227324.6010468184</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>9230572.66837664</t>
+          <t>5715828.923541166</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>62925085.0</t>
+          <t>41341066.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-31.13</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13241,22 +13241,22 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13306,22 +13306,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9124.569</t>
+          <t>2373.75</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,12 +13378,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-46.11</t>
+          <t>-46.72</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13484,12 +13484,12 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -13504,53 +13504,53 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>28.61</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>34.69</v>
+        <v>34.05</v>
       </c>
       <c r="AN31" t="n">
-        <v>35.02</v>
+        <v>34.84</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-98.17</t>
+          <t>-82.56</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-124.36</t>
+          <t>-130.69</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>234002523.4892704</t>
+          <t>233694384.6492857</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>247188336.0</t>
+          <t>62925085.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
@@ -13596,17 +13596,17 @@
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-2588977.629251604</t>
+          <t>-770585.2757703357</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>11609398.38712816</t>
+          <t>9230572.66837664</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>247188336.0</t>
+          <t>62925085.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-30.33</t>
+          <t>-31.13</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -13681,12 +13681,12 @@
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13741,17 +13741,17 @@
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13773,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-11.05</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1253.701</t>
+          <t>9124.569</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-44.36</t>
+          <t>-46.11</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13914,12 +13914,12 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -13929,58 +13929,58 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-13.73</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>35.38</v>
+        <v>34.69</v>
       </c>
       <c r="AN32" t="n">
-        <v>35.18</v>
+        <v>35.02</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-98.17</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-118.38</t>
+          <t>-124.36</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>234002523.4892704</t>
+          <t>233694384.6492857</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>34037781.0</t>
+          <t>247188336.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
@@ -14026,17 +14026,17 @@
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-5170500.541320652</t>
+          <t>-2588977.629251604</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-5149391.707052823</t>
+          <t>11609398.38712816</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>34037781.0</t>
+          <t>247188336.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-28.08</t>
+          <t>-30.33</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14101,22 +14101,22 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -14166,22 +14166,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-11.05</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>804.084</t>
+          <t>1253.701</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14238,12 +14238,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-13.35</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-38.22</t>
+          <t>-44.36</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,12 +14323,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -14344,12 +14344,12 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -14359,58 +14359,58 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-13.73</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>35.96</v>
+        <v>35.38</v>
       </c>
       <c r="AN33" t="n">
-        <v>35.33</v>
+        <v>35.18</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-103.95</t>
+          <t>-108.86</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-113.38</t>
+          <t>-118.38</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>234002523.4892704</t>
+          <t>233694384.6492857</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>24242908.0</t>
+          <t>34037781.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
@@ -14456,17 +14456,17 @@
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-5174338.51118753</t>
+          <t>-5170500.541320652</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-6069054.102059469</t>
+          <t>-5149391.707052823</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>24242908.0</t>
+          <t>34037781.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-20.13</t>
+          <t>-28.08</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>804.084</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14668,12 +14668,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-25.75</t>
+          <t>-15.52</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-31.45</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14753,17 +14753,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14774,17 +14774,17 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -14794,53 +14794,53 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>33.60000000000001</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>36.37</v>
+        <v>35.96</v>
       </c>
       <c r="AN34" t="n">
-        <v>35.42</v>
+        <v>35.33</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-102.12</t>
+          <t>-103.95</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-109.90</t>
+          <t>-113.38</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>234002523.4892704</t>
+          <t>233694384.6492857</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24242908.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
@@ -14886,17 +14886,17 @@
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-5011662.949210814</t>
+          <t>-5174338.51118753</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-5918603.298963025</t>
+          <t>-6069054.102059469</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24242908.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-20.13</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14971,12 +14971,12 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -15001,12 +15001,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/風機維護.xlsx
+++ b/Result/checksun_type/風機維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1130.918</t>
+          <t>1347.469</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-49.63</t>
+          <t>-39.94</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.75</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.27</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>44.65</v>
+        <v>44.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.66</v>
+        <v>46.56</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.72</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-14.01</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-173.49</t>
+          <t>-175.31</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>37660141.4</v>
+        <v>38245237.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>74772185.0</t>
+          <t>63682089.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>81458753.88</v>
+        <v>81578099.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-37112043</t>
+          <t>-25436852</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3026572.764576255</t>
+          <t>-4630586.329104355</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-14797142.43507398</t>
+          <t>-13452660.9340089</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>495.163</t>
+          <t>1130.918</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-59.35</t>
+          <t>-49.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>78.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.20</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>44.99</v>
+        <v>44.65</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.76</v>
+        <v>46.66</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-14.01</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-170.91</t>
+          <t>-173.49</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>37373891.4</v>
+        <v>37660141.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>91945361.2</t>
+          <t>74772185.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>81397712.23999999</v>
+        <v>81458753.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-54571469</t>
+          <t>-37112043</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-886469.1881221232</t>
+          <t>-3026572.764576255</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-15268224.31391429</t>
+          <t>-14797142.43507398</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>754.379</t>
+          <t>495.163</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-64.70</t>
+          <t>-59.35</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>45.3</v>
+        <v>44.99</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.87</v>
+        <v>46.76</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-167.12</t>
+          <t>-170.91</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>46398517.8</v>
+        <v>37373891.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>131458358.1</t>
+          <t>91945361.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>82367727.08</v>
+        <v>81397712.23999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-85059840</t>
+          <t>-54571469</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1728395.380203726</t>
+          <t>-886469.1881221232</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-12563936.95104639</t>
+          <t>-15268224.31391429</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>894.804</t>
+          <t>754.379</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-64.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>45.63</v>
+        <v>45.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.99</v>
+        <v>46.87</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-32.08</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-161.74</t>
+          <t>-167.12</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>56607545.4</v>
+        <v>46398517.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>134181709.8</t>
+          <t>131458358.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>82624485.31999999</v>
+        <v>82367727.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-77574164</t>
+          <t>-85059840</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>4327001.258612839</t>
+          <t>1728395.380203726</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9404152.255840585</t>
+          <t>-12563936.95104639</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1280.793</t>
+          <t>894.804</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-35.80</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>45.99</v>
+        <v>45.63</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.13</v>
+        <v>46.99</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-60.10</t>
+          <t>-45.39</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-154.73</t>
+          <t>-161.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>89118941.40000001</v>
+        <v>56607545.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>138816628.8</t>
+          <t>134181709.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>83437284.84</v>
+        <v>82624485.31999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-49697687</t>
+          <t>-77574164</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>6823574.624877097</t>
+          <t>4327001.258612839</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-5128552.57498084</t>
+          <t>-9404152.255840585</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1105.216</t>
+          <t>1280.793</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.44</t>
+          <t>-35.80</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>46.37</v>
+        <v>45.99</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.28</v>
+        <v>47.13</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-60.10</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-146.51</t>
+          <t>-154.73</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>111884228.6</v>
+        <v>89118941.40000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>138885693.6</t>
+          <t>138816628.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>83731647.22</v>
+        <v>83437284.84</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-27001465</t>
+          <t>-49697687</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>8996688.661214905</t>
+          <t>6823574.624877097</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-550614.5817890316</t>
+          <t>-5128552.57498084</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1580.018</t>
+          <t>1105.216</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>46.82</v>
+        <v>46.37</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.42</v>
+        <v>47.28</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-113.18</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-137.01</t>
+          <t>-146.51</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>146516831</v>
+        <v>111884228.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>138891629.3</t>
+          <t>138885693.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>86052402.7</v>
+        <v>83731647.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7625201</t>
+          <t>-27001465</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>10732561.97812471</t>
+          <t>8996688.661214905</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6770002.28640601</t>
+          <t>-550614.5817890316</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>47.27</v>
+        <v>46.82</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.55</v>
+        <v>47.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>216518198.4</v>
+        <v>146516831</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>85485799.7</v>
+        <v>86052402.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>14830238.83788446</t>
+          <t>6770002.28640601</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>47.72</v>
+        <v>47.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.67</v>
+        <v>47.55</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>211755874.2</v>
+        <v>216518198.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>84907732.44</v>
+        <v>85485799.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>24028515.4529292</t>
+          <t>14830238.83788446</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>48.22</v>
+        <v>47.72</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.82</v>
+        <v>47.67</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>188514316.2</v>
+        <v>211755874.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>82208595.36</v>
+        <v>84907732.44</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>23788810.95824565</t>
+          <t>24028515.4529292</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>48.6</v>
+        <v>48.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.92</v>
+        <v>47.82</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>165887158.6</v>
+        <v>188514316.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>79329370.94</v>
+        <v>82208595.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>26104681.14590324</t>
+          <t>23788810.95824565</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1488.337</t>
+          <t>1116.892</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-48.94</t>
+          <t>-53.69</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.82</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>48.49</t>
+          <t>45.04</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-15.58</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-13.13</t>
+          <t>-14.54</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>46.56</v>
+        <v>45.52</v>
       </c>
       <c r="AN13" t="n">
-        <v>53.6</v>
+        <v>53.27</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>56.99</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-146.93</t>
+          <t>-147.36</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>823371476.5879829</t>
+          <t>822287936.4535714</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>58724698.0</t>
+          <t>43262255.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>68604761.59999999</v>
+        <v>60698958.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>134363485.4</t>
+          <t>131072655.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-65758723</t>
+          <t>-70373696</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>871517.0457014539</t>
+          <t>-1369222.86851518</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-11097576.5763482</t>
+          <t>-13693292.39670667</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>58724698.0</t>
+          <t>43262255.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1193.144</t>
+          <t>1488.337</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-34.10</t>
+          <t>-48.94</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>48.49</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-17.28</t>
+          <t>-15.58</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-11.66</t>
+          <t>-13.13</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.41</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>47.64</v>
+        <v>46.56</v>
       </c>
       <c r="AN14" t="n">
-        <v>53.93</v>
+        <v>53.6</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-146.12</t>
+          <t>-146.93</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,20 +6260,20 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>823371476.5879829</t>
+          <t>822287936.4535714</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>47864486.0</t>
+          <t>58724698.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>87822165.2</v>
+        <v>68604761.59999999</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>133257287.4</t>
+          <t>134363485.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-45435122</t>
+          <t>-65758723</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>3047715.886074118</t>
+          <t>871517.0457014539</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-8649759.419537961</t>
+          <t>-11097576.5763482</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>47864486.0</t>
+          <t>58724698.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2106.06</t>
+          <t>1193.144</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.10</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-76.88</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>37.27</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-19.77</t>
+          <t>-17.28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-10.35</t>
+          <t>-11.66</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.01000000000001</t>
+          <t>39.41</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>48.62</v>
+        <v>47.64</v>
       </c>
       <c r="AN15" t="n">
-        <v>54.24</v>
+        <v>53.93</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.61</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-18.89</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-144.82</t>
+          <t>-146.12</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,20 +6690,20 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>823371476.5879829</t>
+          <t>822287936.4535714</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>103153046</v>
+        <v>87822165.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133257287.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
@@ -6711,22 +6711,22 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-45435122</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>5174529.578003587</t>
+          <t>3047715.886074118</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3680363.644825548</t>
+          <t>-8649759.419537961</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1860.309</t>
+          <t>2106.06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-77.97</t>
+          <t>-76.88</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>12.77</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>-19.77</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-10.35</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>39.01000000000001</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>49.61</v>
+        <v>48.62</v>
       </c>
       <c r="AN16" t="n">
-        <v>54.55</v>
+        <v>54.24</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>58.61</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-28.62</t>
+          <t>-18.89</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-142.70</t>
+          <t>-144.82</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,16 +7120,16 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>823371476.5879829</t>
+          <t>822287936.4535714</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70285205.0</t>
+          <t>83358150.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>116746722.4</v>
+        <v>103153046</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
@@ -7146,17 +7146,17 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>6784510.163972521</t>
+          <t>5174529.578003587</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-252677.836492613</t>
+          <t>-3680363.644825548</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>70285205.0</t>
+          <t>83358150.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-35.92</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>40.35</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>38.5</t>
         </is>
       </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>37.15</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2129.764</t>
+          <t>1860.309</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-77.97</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-22.16</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>50.62</v>
+        <v>49.61</v>
       </c>
       <c r="AN17" t="n">
-        <v>54.92</v>
+        <v>54.55</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-36.90</t>
+          <t>-28.62</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-139.64</t>
+          <t>-142.70</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,16 +7550,16 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>823371476.5879829</t>
+          <t>822287936.4535714</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>82791269.0</t>
+          <t>70285205.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>201446352.6</v>
+        <v>116746722.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
@@ -7576,17 +7576,17 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>8063998.891329818</t>
+          <t>6784510.163972521</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>6053713.06242919</t>
+          <t>-252677.836492613</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>82791269.0</t>
+          <t>70285205.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-36.58</t>
+          <t>-35.92</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3909.656</t>
+          <t>2129.764</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-77.19</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-22.16</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>51.71</v>
+        <v>50.62</v>
       </c>
       <c r="AN18" t="n">
-        <v>55.28</v>
+        <v>54.92</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-45.17</t>
+          <t>-36.90</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-135.99</t>
+          <t>-139.64</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,16 +7980,16 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>823371476.5879829</t>
+          <t>822287936.4535714</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>154811716.0</t>
+          <t>82791269.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>200122209.2</v>
+        <v>201446352.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
@@ -8006,17 +8006,17 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>8429505.405675387</t>
+          <t>8063998.891329818</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>13506703.45151642</t>
+          <t>6053713.06242919</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>154811716.0</t>
+          <t>82791269.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-33.67</t>
+          <t>-36.58</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3220.761</t>
+          <t>3909.656</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-77.99</t>
+          <t>-77.19</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-23.04</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>52.74</v>
+        <v>51.71</v>
       </c>
       <c r="AN19" t="n">
-        <v>55.61</v>
+        <v>55.28</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-58.77</t>
+          <t>-45.17</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-131.92</t>
+          <t>-135.99</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,16 +8410,16 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>823371476.5879829</t>
+          <t>822287936.4535714</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>124518890.0</t>
+          <t>154811716.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>178692409.6</v>
+        <v>200122209.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
@@ -8436,17 +8436,17 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>7506378.488249744</t>
+          <t>8429505.405675387</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>15954973.84837258</t>
+          <t>13506703.45151642</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>124518890.0</t>
+          <t>154811716.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-33.67</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3762.915</t>
+          <t>3220.761</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-77.45</t>
+          <t>-77.99</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-20.71</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>42.70999999999999</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>53.86</v>
+        <v>52.74</v>
       </c>
       <c r="AN20" t="n">
-        <v>55.96</v>
+        <v>55.61</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>61.35</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-70.84</t>
+          <t>-58.77</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-127.23</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,16 +8840,16 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>823371476.5879829</t>
+          <t>822287936.4535714</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>151326532.0</t>
+          <t>124518890.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>178692409.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
@@ -8866,17 +8866,17 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>5970270.240954683</t>
+          <t>7506378.488249744</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>22128342.42072523</t>
+          <t>15954973.84837258</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>151326532.0</t>
+          <t>124518890.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-34.42</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8946,17 +8946,17 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11938.065</t>
+          <t>3762.915</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-76.28</t>
+          <t>-77.45</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,17 +9184,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-20.71</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>42.70999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>54.97</v>
+        <v>53.86</v>
       </c>
       <c r="AN21" t="n">
-        <v>56.3</v>
+        <v>55.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.35</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-85.23</t>
+          <t>-70.84</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-122.41</t>
+          <t>-127.23</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>823371476.5879829</t>
+          <t>822287936.4535714</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>493783356.0</t>
+          <t>151326532.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
@@ -9296,17 +9296,17 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>3032438.935541857</t>
+          <t>5970270.240954683</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>27284895.0804888</t>
+          <t>22128342.42072523</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>493783356.0</t>
+          <t>151326532.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-34.42</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1918.658</t>
+          <t>11938.065</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-77.25</t>
+          <t>-76.28</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-16.90</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-9.04</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>44.64</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>55.96</v>
+        <v>54.97</v>
       </c>
       <c r="AN22" t="n">
-        <v>56.57</v>
+        <v>56.3</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-107.56</t>
+          <t>-85.23</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-117.63</t>
+          <t>-122.41</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>823371476.5879829</t>
+          <t>822287936.4535714</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>76170552.0</t>
+          <t>493783356.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1377098.545357588</t>
+          <t>3032438.935541857</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-3014864.229866385</t>
+          <t>27284895.0804888</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>76170552.0</t>
+          <t>493783356.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-33.83</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9871,17 +9871,17 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-11.08</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1080.792</t>
+          <t>1918.658</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-12.21</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-74.73</t>
+          <t>-77.25</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,12 +10023,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-13.47</t>
+          <t>-16.90</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.34</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>57.02</v>
+        <v>55.96</v>
       </c>
       <c r="AN23" t="n">
-        <v>56.89</v>
+        <v>56.57</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>62.94</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-117.71</t>
+          <t>-107.56</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-112.89</t>
+          <t>-117.63</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>823371476.5879829</t>
+          <t>822287936.4535714</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>47662718.0</t>
+          <t>76170552.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
@@ -10156,17 +10156,17 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1079322.966355988</t>
+          <t>-1377098.545357588</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1448331.950735688</t>
+          <t>-3014864.229866385</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>47662718.0</t>
+          <t>76170552.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-26.50</t>
+          <t>-33.83</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>465.71</t>
+          <t>422.572</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-69.34</t>
+          <t>-70.11</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-46.52</t>
+          <t>-47.44</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10474,73 +10474,73 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>45.97</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-12.66</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>30.07</v>
+        <v>29.51</v>
       </c>
       <c r="AN24" t="n">
-        <v>33.64</v>
+        <v>33.48</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-158.82</t>
+          <t>-159.66</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10560,20 +10560,20 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>233694384.6492857</t>
+          <t>233384336.4072753</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>12203557.0</t>
+          <t>10900378.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>15249414.8</v>
+        <v>14176321.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>49734645.5</t>
+          <t>47420905.2</t>
         </is>
       </c>
       <c r="AZ24" t="n">
@@ -10581,22 +10581,22 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-34485230</t>
+          <t>-33244583</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-2625970.797883155</t>
+          <t>-3395577.24606554</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-7096497.490293983</t>
+          <t>-7628412.71106866</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>12203557.0</t>
+          <t>10900378.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-32.05</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10671,12 +10671,12 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10726,22 +10726,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>612.432</t>
+          <t>465.71</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-60.87</t>
+          <t>-69.34</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-45.49</t>
+          <t>-46.52</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10904,73 +10904,73 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>70.27</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-14.68</t>
+          <t>-12.66</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>30.62</v>
+        <v>30.07</v>
       </c>
       <c r="AN25" t="n">
-        <v>33.79</v>
+        <v>33.64</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-157.54</t>
+          <t>-158.82</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10990,20 +10990,20 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>233694384.6492857</t>
+          <t>233384336.4072753</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>16262559.0</t>
+          <t>12203557.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>19930126</v>
+        <v>15249414.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>50938580.6</t>
+          <t>49734645.5</t>
         </is>
       </c>
       <c r="AZ25" t="n">
@@ -11011,22 +11011,22 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-31008454</t>
+          <t>-34485230</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-1813147.762899367</t>
+          <t>-2625970.797883155</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-6222798.585962512</t>
+          <t>-7096497.490293983</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>16262559.0</t>
+          <t>12203557.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-29.54</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
@@ -11091,22 +11091,22 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -11156,22 +11156,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>649.691</t>
+          <t>612.432</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-60.87</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-44.67</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11313,17 +11313,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11334,73 +11334,73 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>70.27</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-14.68</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-9.4</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>31.12</v>
+        <v>30.62</v>
       </c>
       <c r="AN26" t="n">
-        <v>33.95</v>
+        <v>33.79</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-155.61</t>
+          <t>-157.54</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11420,20 +11420,20 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>233694384.6492857</t>
+          <t>233384336.4072753</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>24945827.4</v>
+        <v>19930126</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50938580.6</t>
         </is>
       </c>
       <c r="AZ26" t="n">
@@ -11441,22 +11441,22 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31008454</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-1011393.067796977</t>
+          <t>-1813147.762899367</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-5187307.558847457</t>
+          <t>-6222798.585962512</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-28.48</t>
+          <t>-29.54</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="BM26" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN26" t="inlineStr">
@@ -11521,22 +11521,22 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>547.074</t>
+          <t>649.691</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11658,12 +11658,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-46.41</t>
+          <t>-44.67</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11764,73 +11764,73 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-18.87</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>25.66</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>31.63</v>
+        <v>31.12</v>
       </c>
       <c r="AN27" t="n">
-        <v>34.09</v>
+        <v>33.95</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-32.22</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-152.71</t>
+          <t>-155.61</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11850,16 +11850,16 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>233694384.6492857</t>
+          <t>233384336.4072753</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>14123190.0</t>
+          <t>17391925.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>34052459.4</v>
+        <v>24945827.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
@@ -11876,17 +11876,17 @@
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-252135.8876059811</t>
+          <t>-1011393.067796977</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-3643777.178724259</t>
+          <t>-5187307.558847457</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>14123190.0</t>
+          <t>17391925.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-28.48</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="BM27" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN27" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -12016,22 +12016,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>642.086</t>
+          <t>547.074</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-47.85</t>
+          <t>-46.41</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12194,63 +12194,63 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-20.16</t>
+          <t>-18.87</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>25.66</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>32.18</v>
+        <v>31.63</v>
       </c>
       <c r="AN28" t="n">
-        <v>34.27</v>
+        <v>34.09</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>-32.22</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-148.47</t>
+          <t>-152.71</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12280,16 +12280,16 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>233694384.6492857</t>
+          <t>233384336.4072753</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>16265843.0</t>
+          <t>14123190.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>80665488.59999999</v>
+        <v>34052459.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
@@ -12306,17 +12306,17 @@
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>364526.165324615</t>
+          <t>-252135.8876059811</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-958377.2721652538</t>
+          <t>-3643777.178724259</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>16265843.0</t>
+          <t>14123190.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-32.58</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="BM28" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN28" t="inlineStr">
@@ -12381,22 +12381,22 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12446,22 +12446,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1398.834</t>
+          <t>642.086</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-47.95</t>
+          <t>-47.85</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12603,17 +12603,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12624,73 +12624,73 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-20.62</t>
+          <t>-20.16</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>32.79</v>
+        <v>32.18</v>
       </c>
       <c r="AN29" t="n">
-        <v>34.46</v>
+        <v>34.27</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.77</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-55.82</t>
+          <t>-44.01</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-143.13</t>
+          <t>-148.47</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12710,16 +12710,16 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>233694384.6492857</t>
+          <t>233384336.4072753</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>35607113.0</t>
+          <t>16265843.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>84219876.2</v>
+        <v>80665488.59999999</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
@@ -12736,17 +12736,17 @@
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>605054.0630500456</t>
+          <t>364526.165324615</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>2682566.104067795</t>
+          <t>-958377.2721652538</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>35607113.0</t>
+          <t>16265843.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-32.72</t>
+          <t>-32.58</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="BM29" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN29" t="inlineStr">
@@ -12811,12 +12811,12 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1600.961</t>
+          <t>1398.834</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-48.16</t>
+          <t>-47.95</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13054,73 +13054,73 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.62</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>33.41</v>
+        <v>32.79</v>
       </c>
       <c r="AN30" t="n">
-        <v>34.66</v>
+        <v>34.46</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-69.23</t>
+          <t>-55.82</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-143.13</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13140,16 +13140,16 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>233694384.6492857</t>
+          <t>233384336.4072753</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>41341066.0</t>
+          <t>35607113.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>81947035.2</v>
+        <v>84219876.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
@@ -13166,17 +13166,17 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>227324.6010468184</t>
+          <t>605054.0630500456</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>5715828.923541166</t>
+          <t>2682566.104067795</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>41341066.0</t>
+          <t>35607113.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-32.72</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="BM30" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN30" t="inlineStr">
@@ -13241,22 +13241,22 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13306,22 +13306,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2373.75</t>
+          <t>1600.961</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,12 +13378,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-46.72</t>
+          <t>-48.16</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13484,12 +13484,12 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -13504,53 +13504,53 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>34.05</v>
+        <v>33.41</v>
       </c>
       <c r="AN31" t="n">
-        <v>34.84</v>
+        <v>34.66</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-82.56</t>
+          <t>-69.23</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-130.69</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13570,16 +13570,16 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>233694384.6492857</t>
+          <t>233384336.4072753</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>62925085.0</t>
+          <t>41341066.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>81947035.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
@@ -13596,17 +13596,17 @@
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-770585.2757703357</t>
+          <t>227324.6010468184</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>9230572.66837664</t>
+          <t>5715828.923541166</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>62925085.0</t>
+          <t>41341066.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-31.13</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="BM31" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN31" t="inlineStr">
@@ -13671,22 +13671,22 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13736,22 +13736,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9124.569</t>
+          <t>2373.75</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-46.11</t>
+          <t>-46.72</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13914,12 +13914,12 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -13934,53 +13934,53 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>28.61</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>34.69</v>
+        <v>34.05</v>
       </c>
       <c r="AN32" t="n">
-        <v>35.02</v>
+        <v>34.84</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-98.17</t>
+          <t>-82.56</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-124.36</t>
+          <t>-130.69</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>233694384.6492857</t>
+          <t>233384336.4072753</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>247188336.0</t>
+          <t>62925085.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
@@ -14026,17 +14026,17 @@
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-2588977.629251604</t>
+          <t>-770585.2757703357</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>11609398.38712816</t>
+          <t>9230572.66837664</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>247188336.0</t>
+          <t>62925085.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-30.33</t>
+          <t>-31.13</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="BM32" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN32" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -14111,12 +14111,12 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -14171,17 +14171,17 @@
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14203,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-11.05</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1253.701</t>
+          <t>9124.569</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14238,12 +14238,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-44.36</t>
+          <t>-46.11</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,17 +14323,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14344,12 +14344,12 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -14359,58 +14359,58 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>-13.73</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>35.38</v>
+        <v>34.69</v>
       </c>
       <c r="AN33" t="n">
-        <v>35.18</v>
+        <v>35.02</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-98.17</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-118.38</t>
+          <t>-124.36</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>233694384.6492857</t>
+          <t>233384336.4072753</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>34037781.0</t>
+          <t>247188336.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
@@ -14456,17 +14456,17 @@
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-5170500.541320652</t>
+          <t>-2588977.629251604</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-5149391.707052823</t>
+          <t>11609398.38712816</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>34037781.0</t>
+          <t>247188336.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-28.08</t>
+          <t>-30.33</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="BM33" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN33" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-11.05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>804.084</t>
+          <t>1253.701</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14668,12 +14668,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-15.52</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-38.22</t>
+          <t>-44.36</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14753,12 +14753,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -14774,12 +14774,12 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -14789,58 +14789,58 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-13.73</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>35.96</v>
+        <v>35.38</v>
       </c>
       <c r="AN34" t="n">
-        <v>35.33</v>
+        <v>35.18</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-103.95</t>
+          <t>-108.86</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-113.38</t>
+          <t>-118.38</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>233694384.6492857</t>
+          <t>233384336.4072753</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>24242908.0</t>
+          <t>34037781.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
@@ -14886,17 +14886,17 @@
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-5174338.51118753</t>
+          <t>-5170500.541320652</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-6069054.102059469</t>
+          <t>-5149391.707052823</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>24242908.0</t>
+          <t>34037781.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-20.13</t>
+          <t>-28.08</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14941,7 +14941,7 @@
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
@@ -14971,12 +14971,12 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -15001,12 +15001,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/風機維護.xlsx
+++ b/Result/checksun_type/風機維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1347.469</t>
+          <t>574.591</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-39.94</t>
+          <t>-22.74</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.75</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,42 +1014,42 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1058,29 +1058,29 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>44.27</v>
+        <v>43.87</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.56</v>
+        <v>46.46</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.62</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-175.31</t>
+          <t>-176.43</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>55608632.0</t>
+          <t>23632608.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>38245237.2</v>
+        <v>35633146.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>63682089.3</t>
+          <t>46120346.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>81578099.64</v>
+        <v>81185268.44</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-25436852</t>
+          <t>-10487199</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4630586.329104355</t>
+          <t>-6160251.379998012</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-13452660.9340089</t>
+          <t>-14573409.15991313</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>55608632.0</t>
+          <t>23632608.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1130.918</t>
+          <t>1347.469</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-49.63</t>
+          <t>-39.94</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.75</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>78.27</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>44.65</v>
+        <v>44.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.66</v>
+        <v>46.56</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.72</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-14.01</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-173.49</t>
+          <t>-175.31</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>37660141.4</v>
+        <v>38245237.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>74772185.0</t>
+          <t>63682089.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>81458753.88</v>
+        <v>81578099.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-37112043</t>
+          <t>-25436852</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3026572.764576255</t>
+          <t>-4630586.329104355</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-14797142.43507398</t>
+          <t>-13452660.9340089</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>495.163</t>
+          <t>1130.918</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-59.35</t>
+          <t>-49.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>78.27</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.20</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>44.99</v>
+        <v>44.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.76</v>
+        <v>46.66</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-14.01</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-170.91</t>
+          <t>-173.49</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>37373891.4</v>
+        <v>37660141.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>91945361.2</t>
+          <t>74772185.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>81397712.23999999</v>
+        <v>81458753.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-54571469</t>
+          <t>-37112043</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-886469.1881221232</t>
+          <t>-3026572.764576255</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-15268224.31391429</t>
+          <t>-14797142.43507398</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>754.379</t>
+          <t>495.163</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-64.70</t>
+          <t>-59.35</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>45.3</v>
+        <v>44.99</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.87</v>
+        <v>46.76</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-167.12</t>
+          <t>-170.91</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>46398517.8</v>
+        <v>37373891.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>131458358.1</t>
+          <t>91945361.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>82367727.08</v>
+        <v>81397712.23999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-85059840</t>
+          <t>-54571469</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1728395.380203726</t>
+          <t>-886469.1881221232</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-12563936.95104639</t>
+          <t>-15268224.31391429</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>894.804</t>
+          <t>754.379</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-64.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>45.63</v>
+        <v>45.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.99</v>
+        <v>46.87</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-32.08</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-161.74</t>
+          <t>-167.12</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>56607545.4</v>
+        <v>46398517.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>134181709.8</t>
+          <t>131458358.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>82624485.31999999</v>
+        <v>82367727.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-77574164</t>
+          <t>-85059840</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4327001.258612839</t>
+          <t>1728395.380203726</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9404152.255840585</t>
+          <t>-12563936.95104639</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1280.793</t>
+          <t>894.804</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-35.80</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>45.99</v>
+        <v>45.63</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.13</v>
+        <v>46.99</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-60.10</t>
+          <t>-45.39</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-154.73</t>
+          <t>-161.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>89118941.40000001</v>
+        <v>56607545.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>138816628.8</t>
+          <t>134181709.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>83437284.84</v>
+        <v>82624485.31999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-49697687</t>
+          <t>-77574164</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>6823574.624877097</t>
+          <t>4327001.258612839</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-5128552.57498084</t>
+          <t>-9404152.255840585</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1105.216</t>
+          <t>1280.793</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.44</t>
+          <t>-35.80</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>46.37</v>
+        <v>45.99</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.28</v>
+        <v>47.13</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-60.10</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-146.51</t>
+          <t>-154.73</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>111884228.6</v>
+        <v>89118941.40000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>138885693.6</t>
+          <t>138816628.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>83731647.22</v>
+        <v>83437284.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-27001465</t>
+          <t>-49697687</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>8996688.661214905</t>
+          <t>6823574.624877097</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-550614.5817890316</t>
+          <t>-5128552.57498084</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1580.018</t>
+          <t>1105.216</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>46.82</v>
+        <v>46.37</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.42</v>
+        <v>47.28</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-113.18</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-137.01</t>
+          <t>-146.51</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>146516831</v>
+        <v>111884228.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>138891629.3</t>
+          <t>138885693.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>86052402.7</v>
+        <v>83731647.22</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7625201</t>
+          <t>-27001465</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>10732561.97812471</t>
+          <t>8996688.661214905</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>6770002.28640601</t>
+          <t>-550614.5817890316</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>47.27</v>
+        <v>46.82</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.55</v>
+        <v>47.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>216518198.4</v>
+        <v>146516831</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>85485799.7</v>
+        <v>86052402.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>14830238.83788446</t>
+          <t>6770002.28640601</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>47.72</v>
+        <v>47.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.67</v>
+        <v>47.55</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>211755874.2</v>
+        <v>216518198.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>84907732.44</v>
+        <v>85485799.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>24028515.4529292</t>
+          <t>14830238.83788446</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>48.22</v>
+        <v>47.72</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.82</v>
+        <v>47.67</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>188514316.2</v>
+        <v>211755874.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>82208595.36</v>
+        <v>84907732.44</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>23788810.95824565</t>
+          <t>24028515.4529292</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1116.892</t>
+          <t>1019.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-53.69</t>
+          <t>-36.24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-77.82</t>
+          <t>-77.59</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,68 +5744,68 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>45.04</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-14.54</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>45.52</v>
+        <v>44.54</v>
       </c>
       <c r="AN13" t="n">
-        <v>53.27</v>
+        <v>52.9</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>56.99</t>
+          <t>56.44</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-147.36</t>
+          <t>-147.37</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>822287936.4535714</t>
+          <t>821200433.9871612</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>43262255.0</t>
+          <t>39965805.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>60698958.8</v>
+        <v>54635078.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>131072655.7</t>
+          <t>85690900.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-70373696</t>
+          <t>-31055821</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-1369222.86851518</t>
+          <t>-3530141.64428822</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-13693292.39670667</t>
+          <t>-15415194.91103993</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>43262255.0</t>
+          <t>39965805.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-34.83</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1488.337</t>
+          <t>1116.892</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-48.94</t>
+          <t>-53.69</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.82</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>48.49</t>
+          <t>45.04</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-15.58</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-13.13</t>
+          <t>-14.54</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>46.56</v>
+        <v>45.52</v>
       </c>
       <c r="AN14" t="n">
-        <v>53.6</v>
+        <v>53.27</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>56.99</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-146.93</t>
+          <t>-147.36</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,20 +6260,20 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>822287936.4535714</t>
+          <t>821200433.9871612</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>58724698.0</t>
+          <t>43262255.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>68604761.59999999</v>
+        <v>60698958.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>134363485.4</t>
+          <t>131072655.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-65758723</t>
+          <t>-70373696</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>871517.0457014539</t>
+          <t>-1369222.86851518</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-11097576.5763482</t>
+          <t>-13693292.39670667</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>58724698.0</t>
+          <t>43262255.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1193.144</t>
+          <t>1488.337</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-34.10</t>
+          <t>-48.94</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>48.49</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-17.28</t>
+          <t>-15.58</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-11.66</t>
+          <t>-13.13</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.41</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>47.64</v>
+        <v>46.56</v>
       </c>
       <c r="AN15" t="n">
-        <v>53.93</v>
+        <v>53.6</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-146.12</t>
+          <t>-146.93</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,20 +6690,20 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>822287936.4535714</t>
+          <t>821200433.9871612</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>47864486.0</t>
+          <t>58724698.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>87822165.2</v>
+        <v>68604761.59999999</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>133257287.4</t>
+          <t>134363485.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
@@ -6711,22 +6711,22 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-45435122</t>
+          <t>-65758723</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>3047715.886074118</t>
+          <t>871517.0457014539</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-8649759.419537961</t>
+          <t>-11097576.5763482</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>47864486.0</t>
+          <t>58724698.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2106.06</t>
+          <t>1193.144</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-76.88</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>37.27</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-19.77</t>
+          <t>-17.28</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-10.35</t>
+          <t>-11.66</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.01000000000001</t>
+          <t>39.41</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>48.62</v>
+        <v>47.64</v>
       </c>
       <c r="AN16" t="n">
-        <v>54.24</v>
+        <v>53.93</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>58.61</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-18.89</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-144.82</t>
+          <t>-146.12</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,20 +7120,20 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>822287936.4535714</t>
+          <t>821200433.9871612</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>103153046</v>
+        <v>87822165.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133257287.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
@@ -7141,22 +7141,22 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-45435122</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>5174529.578003587</t>
+          <t>3047715.886074118</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3680363.644825548</t>
+          <t>-8649759.419537961</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1860.309</t>
+          <t>2106.06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-77.97</t>
+          <t>-76.88</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>12.77</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>-19.77</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-10.35</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>39.01000000000001</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>49.61</v>
+        <v>48.62</v>
       </c>
       <c r="AN17" t="n">
-        <v>54.55</v>
+        <v>54.24</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>58.61</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-28.62</t>
+          <t>-18.89</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-142.70</t>
+          <t>-144.82</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,16 +7550,16 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>822287936.4535714</t>
+          <t>821200433.9871612</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>70285205.0</t>
+          <t>83358150.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>116746722.4</v>
+        <v>103153046</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
@@ -7576,17 +7576,17 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>6784510.163972521</t>
+          <t>5174529.578003587</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-252677.836492613</t>
+          <t>-3680363.644825548</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>70285205.0</t>
+          <t>83358150.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-35.92</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
+          <t>40.35</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>38.5</t>
         </is>
       </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>37.15</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2129.764</t>
+          <t>1860.309</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-77.97</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-22.16</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>50.62</v>
+        <v>49.61</v>
       </c>
       <c r="AN18" t="n">
-        <v>54.92</v>
+        <v>54.55</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-36.90</t>
+          <t>-28.62</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-139.64</t>
+          <t>-142.70</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,16 +7980,16 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>822287936.4535714</t>
+          <t>821200433.9871612</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>82791269.0</t>
+          <t>70285205.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>201446352.6</v>
+        <v>116746722.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
@@ -8006,17 +8006,17 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>8063998.891329818</t>
+          <t>6784510.163972521</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>6053713.06242919</t>
+          <t>-252677.836492613</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>82791269.0</t>
+          <t>70285205.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-36.58</t>
+          <t>-35.92</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3909.656</t>
+          <t>2129.764</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-77.19</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,17 +8324,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-22.16</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>51.71</v>
+        <v>50.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>55.28</v>
+        <v>54.92</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-45.17</t>
+          <t>-36.90</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-135.99</t>
+          <t>-139.64</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,16 +8410,16 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>822287936.4535714</t>
+          <t>821200433.9871612</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>154811716.0</t>
+          <t>82791269.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>200122209.2</v>
+        <v>201446352.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
@@ -8436,17 +8436,17 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>8429505.405675387</t>
+          <t>8063998.891329818</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>13506703.45151642</t>
+          <t>6053713.06242919</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>154811716.0</t>
+          <t>82791269.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-33.67</t>
+          <t>-36.58</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3220.761</t>
+          <t>3909.656</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-77.99</t>
+          <t>-77.19</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-23.04</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>52.74</v>
+        <v>51.71</v>
       </c>
       <c r="AN20" t="n">
-        <v>55.61</v>
+        <v>55.28</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-58.77</t>
+          <t>-45.17</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-131.92</t>
+          <t>-135.99</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,16 +8840,16 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>822287936.4535714</t>
+          <t>821200433.9871612</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>124518890.0</t>
+          <t>154811716.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>178692409.6</v>
+        <v>200122209.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
@@ -8866,17 +8866,17 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>7506378.488249744</t>
+          <t>8429505.405675387</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>15954973.84837258</t>
+          <t>13506703.45151642</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>124518890.0</t>
+          <t>154811716.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-33.67</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3762.915</t>
+          <t>3220.761</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-77.45</t>
+          <t>-77.99</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-20.71</t>
+          <t>-23.04</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>42.70999999999999</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>53.86</v>
+        <v>52.74</v>
       </c>
       <c r="AN21" t="n">
-        <v>55.96</v>
+        <v>55.61</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>61.35</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-70.84</t>
+          <t>-58.77</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-127.23</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,16 +9270,16 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>822287936.4535714</t>
+          <t>821200433.9871612</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>151326532.0</t>
+          <t>124518890.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>178692409.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
@@ -9296,17 +9296,17 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>5970270.240954683</t>
+          <t>7506378.488249744</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>22128342.42072523</t>
+          <t>15954973.84837258</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>151326532.0</t>
+          <t>124518890.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-34.42</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9376,17 +9376,17 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11938.065</t>
+          <t>3762.915</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-76.28</t>
+          <t>-77.45</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,17 +9614,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-20.71</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>42.70999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>54.97</v>
+        <v>53.86</v>
       </c>
       <c r="AN22" t="n">
-        <v>56.3</v>
+        <v>55.96</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.35</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-85.23</t>
+          <t>-70.84</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-122.41</t>
+          <t>-127.23</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>822287936.4535714</t>
+          <t>821200433.9871612</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>493783356.0</t>
+          <t>151326532.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>3032438.935541857</t>
+          <t>5970270.240954683</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>27284895.0804888</t>
+          <t>22128342.42072523</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>493783356.0</t>
+          <t>151326532.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-34.42</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1918.658</t>
+          <t>11938.065</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-77.25</t>
+          <t>-76.28</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-16.90</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-9.04</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>44.64</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>55.96</v>
+        <v>54.97</v>
       </c>
       <c r="AN23" t="n">
-        <v>56.57</v>
+        <v>56.3</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-107.56</t>
+          <t>-85.23</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-117.63</t>
+          <t>-122.41</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>822287936.4535714</t>
+          <t>821200433.9871612</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>76170552.0</t>
+          <t>493783356.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
@@ -10156,17 +10156,17 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1377098.545357588</t>
+          <t>3032438.935541857</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-3014864.229866385</t>
+          <t>27284895.0804888</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>76170552.0</t>
+          <t>493783356.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-33.83</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>422.572</t>
+          <t>418.856</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-70.11</t>
+          <t>-43.13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-47.44</t>
+          <t>-46.52</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10474,73 +10474,73 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>45.97</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-12.88</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.29</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>29.51</v>
+        <v>29.03</v>
       </c>
       <c r="AN24" t="n">
-        <v>33.48</v>
+        <v>33.32</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-159.66</t>
+          <t>-159.87</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10560,20 +10560,20 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>233384336.4072753</t>
+          <t>233075151.0854701</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>10900378.0</t>
+          <t>10890827.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>14176321.8</v>
+        <v>13529849.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>47420905.2</t>
+          <t>23791154.3</t>
         </is>
       </c>
       <c r="AZ24" t="n">
@@ -10581,22 +10581,22 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-33244583</t>
+          <t>-10261305</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-3395577.24606554</t>
+          <t>-4074836.034799184</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-7628412.71106866</t>
+          <t>-7810759.372834224</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>10900378.0</t>
+          <t>10890827.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-32.05</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10661,22 +10661,22 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10726,22 +10726,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>465.71</t>
+          <t>422.572</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10798,102 +10798,102 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>-1.24</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-70.11</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2025-07-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>61.4</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-47.44</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>-16.29</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
           <t>-2.34</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-69.34</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2025-07-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2025-07-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>61.8</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>-46.52</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>-16.29</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>-1.72</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10904,73 +10904,73 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>45.97</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-12.66</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>30.07</v>
+        <v>29.51</v>
       </c>
       <c r="AN25" t="n">
-        <v>33.64</v>
+        <v>33.48</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-158.82</t>
+          <t>-159.66</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10990,20 +10990,20 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>233384336.4072753</t>
+          <t>233075151.0854701</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>12203557.0</t>
+          <t>10900378.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>15249414.8</v>
+        <v>14176321.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>49734645.5</t>
+          <t>47420905.2</t>
         </is>
       </c>
       <c r="AZ25" t="n">
@@ -11011,22 +11011,22 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-34485230</t>
+          <t>-33244583</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-2625970.797883155</t>
+          <t>-3395577.24606554</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-7096497.490293983</t>
+          <t>-7628412.71106866</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>12203557.0</t>
+          <t>10900378.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-32.05</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -11101,12 +11101,12 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -11156,22 +11156,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>612.432</t>
+          <t>465.71</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-60.87</t>
+          <t>-69.34</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-45.49</t>
+          <t>-46.52</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11313,17 +11313,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11334,73 +11334,73 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>70.27</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-14.68</t>
+          <t>-12.66</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>30.62</v>
+        <v>30.07</v>
       </c>
       <c r="AN26" t="n">
-        <v>33.79</v>
+        <v>33.64</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-157.54</t>
+          <t>-158.82</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11420,20 +11420,20 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>233384336.4072753</t>
+          <t>233075151.0854701</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>16262559.0</t>
+          <t>12203557.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>19930126</v>
+        <v>15249414.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>50938580.6</t>
+          <t>49734645.5</t>
         </is>
       </c>
       <c r="AZ26" t="n">
@@ -11441,22 +11441,22 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-31008454</t>
+          <t>-34485230</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-1813147.762899367</t>
+          <t>-2625970.797883155</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-6222798.585962512</t>
+          <t>-7096497.490293983</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>16262559.0</t>
+          <t>12203557.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-29.54</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11521,22 +11521,22 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>649.691</t>
+          <t>612.432</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11658,17 +11658,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-60.87</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-44.67</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11764,73 +11764,73 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>70.27</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-14.68</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-9.4</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>31.12</v>
+        <v>30.62</v>
       </c>
       <c r="AN27" t="n">
-        <v>33.95</v>
+        <v>33.79</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-155.61</t>
+          <t>-157.54</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11850,20 +11850,20 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>233384336.4072753</t>
+          <t>233075151.0854701</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>24945827.4</v>
+        <v>19930126</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50938580.6</t>
         </is>
       </c>
       <c r="AZ27" t="n">
@@ -11871,22 +11871,22 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31008454</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-1011393.067796977</t>
+          <t>-1813147.762899367</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-5187307.558847457</t>
+          <t>-6222798.585962512</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-28.48</t>
+          <t>-29.54</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11951,22 +11951,22 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -12016,22 +12016,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>547.074</t>
+          <t>649.691</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-46.41</t>
+          <t>-44.67</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12194,73 +12194,73 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-18.87</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>25.66</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>31.63</v>
+        <v>31.12</v>
       </c>
       <c r="AN28" t="n">
-        <v>34.09</v>
+        <v>33.95</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-32.22</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-152.71</t>
+          <t>-155.61</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12280,16 +12280,16 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>233384336.4072753</t>
+          <t>233075151.0854701</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>14123190.0</t>
+          <t>17391925.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>34052459.4</v>
+        <v>24945827.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
@@ -12306,17 +12306,17 @@
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-252135.8876059811</t>
+          <t>-1011393.067796977</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-3643777.178724259</t>
+          <t>-5187307.558847457</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>14123190.0</t>
+          <t>17391925.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-28.48</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12446,22 +12446,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>642.086</t>
+          <t>547.074</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-47.85</t>
+          <t>-46.41</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12603,17 +12603,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12624,63 +12624,63 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-20.16</t>
+          <t>-18.87</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>25.66</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>32.18</v>
+        <v>31.63</v>
       </c>
       <c r="AN29" t="n">
-        <v>34.27</v>
+        <v>34.09</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>-32.22</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-148.47</t>
+          <t>-152.71</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12710,16 +12710,16 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>233384336.4072753</t>
+          <t>233075151.0854701</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>16265843.0</t>
+          <t>14123190.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>80665488.59999999</v>
+        <v>34052459.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
@@ -12736,17 +12736,17 @@
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>364526.165324615</t>
+          <t>-252135.8876059811</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-958377.2721652538</t>
+          <t>-3643777.178724259</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>16265843.0</t>
+          <t>14123190.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-32.58</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12811,22 +12811,22 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1398.834</t>
+          <t>642.086</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-47.95</t>
+          <t>-47.85</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13054,73 +13054,73 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-20.62</t>
+          <t>-20.16</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>32.79</v>
+        <v>32.18</v>
       </c>
       <c r="AN30" t="n">
-        <v>34.46</v>
+        <v>34.27</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.77</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-55.82</t>
+          <t>-44.01</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-143.13</t>
+          <t>-148.47</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13140,16 +13140,16 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>233384336.4072753</t>
+          <t>233075151.0854701</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>35607113.0</t>
+          <t>16265843.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>84219876.2</v>
+        <v>80665488.59999999</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
@@ -13166,17 +13166,17 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>605054.0630500456</t>
+          <t>364526.165324615</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>2682566.104067795</t>
+          <t>-958377.2721652538</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>35607113.0</t>
+          <t>16265843.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-32.72</t>
+          <t>-32.58</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13241,12 +13241,12 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13306,22 +13306,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1600.961</t>
+          <t>1398.834</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,12 +13378,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-48.16</t>
+          <t>-47.95</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13484,73 +13484,73 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.62</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>33.41</v>
+        <v>32.79</v>
       </c>
       <c r="AN31" t="n">
-        <v>34.66</v>
+        <v>34.46</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-69.23</t>
+          <t>-55.82</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-143.13</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13570,16 +13570,16 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>233384336.4072753</t>
+          <t>233075151.0854701</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>41341066.0</t>
+          <t>35607113.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>81947035.2</v>
+        <v>84219876.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
@@ -13596,17 +13596,17 @@
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>227324.6010468184</t>
+          <t>605054.0630500456</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>5715828.923541166</t>
+          <t>2682566.104067795</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>41341066.0</t>
+          <t>35607113.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-32.72</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13671,22 +13671,22 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13736,22 +13736,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2373.75</t>
+          <t>1600.961</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-46.72</t>
+          <t>-48.16</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13914,12 +13914,12 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -13934,53 +13934,53 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>34.05</v>
+        <v>33.41</v>
       </c>
       <c r="AN32" t="n">
-        <v>34.84</v>
+        <v>34.66</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-82.56</t>
+          <t>-69.23</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-130.69</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14000,16 +14000,16 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>233384336.4072753</t>
+          <t>233075151.0854701</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>62925085.0</t>
+          <t>41341066.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>81947035.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
@@ -14026,17 +14026,17 @@
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-770585.2757703357</t>
+          <t>227324.6010468184</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>9230572.66837664</t>
+          <t>5715828.923541166</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>62925085.0</t>
+          <t>41341066.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-31.13</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -14111,12 +14111,12 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -14166,22 +14166,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9124.569</t>
+          <t>2373.75</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14238,12 +14238,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-46.11</t>
+          <t>-46.72</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,17 +14323,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14344,12 +14344,12 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -14364,53 +14364,53 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>28.61</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>34.69</v>
+        <v>34.05</v>
       </c>
       <c r="AN33" t="n">
-        <v>35.02</v>
+        <v>34.84</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-98.17</t>
+          <t>-82.56</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-124.36</t>
+          <t>-130.69</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>233384336.4072753</t>
+          <t>233075151.0854701</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>247188336.0</t>
+          <t>62925085.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
@@ -14456,17 +14456,17 @@
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-2588977.629251604</t>
+          <t>-770585.2757703357</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>11609398.38712816</t>
+          <t>9230572.66837664</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>247188336.0</t>
+          <t>62925085.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-30.33</t>
+          <t>-31.13</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14601,17 +14601,17 @@
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14633,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-11.05</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1253.701</t>
+          <t>9124.569</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14668,12 +14668,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-44.36</t>
+          <t>-46.11</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14753,17 +14753,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14774,12 +14774,12 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -14789,58 +14789,58 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-13.73</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>35.38</v>
+        <v>34.69</v>
       </c>
       <c r="AN34" t="n">
-        <v>35.18</v>
+        <v>35.02</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-98.17</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-118.38</t>
+          <t>-124.36</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>233384336.4072753</t>
+          <t>233075151.0854701</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>34037781.0</t>
+          <t>247188336.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
@@ -14886,17 +14886,17 @@
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-5170500.541320652</t>
+          <t>-2588977.629251604</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-5149391.707052823</t>
+          <t>11609398.38712816</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>34037781.0</t>
+          <t>247188336.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-28.08</t>
+          <t>-30.33</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14971,12 +14971,12 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/風機維護.xlsx
+++ b/Result/checksun_type/風機維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>697.346</t>
+          <t>869.687</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-16.04</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.58</v>
+        <v>-0.36</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2.23</v>
+        <v>-1.27</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>42.25</v>
+        <v>41.88</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.07</v>
+        <v>45.96</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.5</v>
+        <v>-1.43</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.66</v>
+        <v>-1.62</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-173.14</t>
+          <t>-171.08</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>155763268.5891089</t>
+          <t>155619509.154661</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>28887127.0</t>
+          <t>35987726.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>27672720.4</v>
+        <v>30143744</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>32958978.8</t>
+          <t>32888445.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>80464167.98</v>
+        <v>80758886.90000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5286258</t>
+          <t>-2744701</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-9874126.9305539</t>
+          <t>-10123346.95654146</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-12883644.54970483</t>
+          <t>-11494057.09947302</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>28887127.0</t>
+          <t>35987726.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>784.322</t>
+          <t>697.346</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-16.04</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.23</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.22</v>
+        <v>0.58</v>
       </c>
       <c r="AI3" t="n">
-        <v>-3.36</v>
+        <v>-2.23</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>42.64</v>
+        <v>42.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.18</v>
+        <v>46.07</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.71</v>
+        <v>-1.66</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-174.98</t>
+          <t>-173.14</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>155763268.5891089</t>
+          <t>155619509.154661</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>32420259.0</t>
+          <t>28887127.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>33017021.4</v>
+        <v>27672720.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>35338581.4</t>
+          <t>32958978.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>80798522.31999999</v>
+        <v>80464167.98</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2321560</t>
+          <t>-5286258</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-9326941.908890095</t>
+          <t>-9874126.9305539</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-13647860.85183223</t>
+          <t>-12883644.54970483</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>32420259.0</t>
+          <t>28887127.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-8.28</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>540.472</t>
+          <t>784.322</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.60</t>
+          <t>-14.23</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.85</v>
+        <v>0.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>-4.19</v>
+        <v>-3.36</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>43.06</v>
+        <v>42.64</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.27</v>
+        <v>46.18</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.68</v>
+        <v>-1.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.73</v>
+        <v>-1.71</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-176.17</t>
+          <t>-174.98</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>155763268.5891089</t>
+          <t>155619509.154661</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>22418103.0</t>
+          <t>32420259.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>35935241</v>
+        <v>33017021.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>36654566.2</t>
+          <t>35338581.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>80677329.12</v>
+        <v>80798522.31999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-719325</t>
+          <t>-2321560</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-8541320.282900617</t>
+          <t>-9326941.908890095</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-14630724.68159164</t>
+          <t>-13647860.85183223</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>22418103.0</t>
+          <t>32420259.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>756.121</t>
+          <t>540.472</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-13.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.41</v>
+        <v>0.85</v>
       </c>
       <c r="AI5" t="n">
-        <v>-5.03</v>
+        <v>-4.19</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.25</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>43.46</v>
+        <v>43.06</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.36</v>
+        <v>46.27</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.78</v>
+        <v>-1.68</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.75</v>
+        <v>-1.73</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-176.81</t>
+          <t>-176.17</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>155763268.5891089</t>
+          <t>155619509.154661</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31005505.0</t>
+          <t>22418103.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>35567552</v>
+        <v>35935241</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>40983034.9</t>
+          <t>36654566.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>81047113.98</v>
+        <v>80677329.12</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5415482</t>
+          <t>-719325</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-7434155.846774974</t>
+          <t>-8541320.282900617</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-14440630.41404826</t>
+          <t>-14630724.68159164</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>31005505.0</t>
+          <t>22418103.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>574.591</t>
+          <t>756.121</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.74</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.85</v>
+        <v>-0.41</v>
       </c>
       <c r="AI6" t="n">
-        <v>-5.74</v>
+        <v>-5.03</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>43.87</v>
+        <v>43.46</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.46</v>
+        <v>46.36</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.62</t>
+          <t>46.57</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.84</v>
+        <v>-1.78</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.74</v>
+        <v>-1.75</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-176.43</t>
+          <t>-176.81</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>155763268.5891089</t>
+          <t>155619509.154661</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23632608.0</t>
+          <t>31005505.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>35633146.6</v>
+        <v>35567552</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>46120346.0</t>
+          <t>40983034.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>81185268.44</v>
+        <v>81047113.98</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-10487199</t>
+          <t>-5415482</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6160251.379998012</t>
+          <t>-7434155.846774974</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-14573409.15991313</t>
+          <t>-14440630.41404826</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>23632608.0</t>
+          <t>31005505.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1347.469</t>
+          <t>574.591</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-39.94</t>
+          <t>-22.74</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.75</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,38 +3124,38 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.73</v>
+        <v>-0.85</v>
       </c>
       <c r="AI7" t="n">
-        <v>-6.6</v>
+        <v>-5.74</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3164,26 +3164,26 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>44.27</v>
+        <v>43.87</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.56</v>
+        <v>46.46</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.88</v>
+        <v>-1.84</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.71</v>
+        <v>-1.74</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-175.31</t>
+          <t>-176.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>155763268.5891089</t>
+          <t>155619509.154661</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>55608632.0</t>
+          <t>23632608.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>38245237.2</v>
+        <v>35633146.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>63682089.3</t>
+          <t>46120346.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>81578099.64</v>
+        <v>81185268.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-25436852</t>
+          <t>-10487199</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4630586.329104355</t>
+          <t>-6160251.379998012</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-13452660.9340089</t>
+          <t>-14573409.15991313</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>55608632.0</t>
+          <t>23632608.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1130.918</t>
+          <t>1347.469</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-49.63</t>
+          <t>-39.94</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.75</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>78.27</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.29</v>
+        <v>-0.73</v>
       </c>
       <c r="AI8" t="n">
-        <v>-7.32</v>
+        <v>-6.6</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>44.65</v>
+        <v>44.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>46.66</v>
+        <v>46.56</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.72</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-14.01</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.91</v>
+        <v>-1.88</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.67</v>
+        <v>-1.71</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-173.49</t>
+          <t>-175.31</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>155763268.5891089</t>
+          <t>155619509.154661</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>37660141.4</v>
+        <v>38245237.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>74772185.0</t>
+          <t>63682089.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>81458753.88</v>
+        <v>81578099.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-37112043</t>
+          <t>-25436852</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3026572.764576255</t>
+          <t>-4630586.329104355</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-14797142.43507398</t>
+          <t>-13452660.9340089</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>495.163</t>
+          <t>1130.918</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,102 +3862,102 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-49.63</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>48.55</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-13.81</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
           <t>-0.36</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-59.35</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>48.15</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>48.55</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-13.40</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>5.41</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0.73</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>78.27</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.97</v>
+        <v>0.29</v>
       </c>
       <c r="AI9" t="n">
-        <v>-8.199999999999999</v>
+        <v>-7.32</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>44.99</v>
+        <v>44.65</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.76</v>
+        <v>46.66</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-14.01</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.96</v>
+        <v>-1.91</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.61</v>
+        <v>-1.67</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-170.91</t>
+          <t>-173.49</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>155763268.5891089</t>
+          <t>155619509.154661</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>37373891.4</v>
+        <v>37660141.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>91945361.2</t>
+          <t>74772185.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>81397712.23999999</v>
+        <v>81458753.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-54571469</t>
+          <t>-37112043</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-886469.1881221232</t>
+          <t>-3026572.764576255</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-15268224.31391429</t>
+          <t>-14797142.43507398</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>754.379</t>
+          <t>495.163</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-64.70</t>
+          <t>-59.35</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="AI10" t="n">
-        <v>-8.98</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>45.3</v>
+        <v>44.99</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.87</v>
+        <v>46.76</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-2.02</v>
+        <v>-1.96</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.53</v>
+        <v>-1.61</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-167.12</t>
+          <t>-170.91</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>155763268.5891089</t>
+          <t>155619509.154661</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>46398517.8</v>
+        <v>37373891.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>131458358.1</t>
+          <t>91945361.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>82367727.08</v>
+        <v>81397712.23999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-85059840</t>
+          <t>-54571469</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1728395.380203726</t>
+          <t>-886469.1881221232</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-12563936.95104639</t>
+          <t>-15268224.31391429</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>894.804</t>
+          <t>754.379</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-64.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.36</v>
+        <v>0.65</v>
       </c>
       <c r="AI11" t="n">
-        <v>-9.82</v>
+        <v>-8.98</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>45.63</v>
+        <v>45.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.99</v>
+        <v>46.87</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-32.08</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-2.04</v>
+        <v>-2.02</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.41</v>
+        <v>-1.53</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-161.74</t>
+          <t>-167.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>155763268.5891089</t>
+          <t>155619509.154661</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>56607545.4</v>
+        <v>46398517.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>134181709.8</t>
+          <t>131458358.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>82624485.31999999</v>
+        <v>82367727.08</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-77574164</t>
+          <t>-85059840</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4327001.258612839</t>
+          <t>1728395.380203726</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-9404152.255840585</t>
+          <t>-12563936.95104639</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1280.793</t>
+          <t>894.804</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-35.80</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.51</v>
+        <v>-0.36</v>
       </c>
       <c r="AI12" t="n">
-        <v>-10.87</v>
+        <v>-9.82</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>45.99</v>
+        <v>45.63</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.13</v>
+        <v>46.99</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-60.10</t>
+          <t>-45.39</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.99</v>
+        <v>-2.04</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.25</v>
+        <v>-1.41</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-154.73</t>
+          <t>-161.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>155763268.5891089</t>
+          <t>155619509.154661</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>89118941.40000001</v>
+        <v>56607545.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>138816628.8</t>
+          <t>134181709.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>83437284.84</v>
+        <v>82624485.31999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-49697687</t>
+          <t>-77574164</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>6823574.624877097</t>
+          <t>4327001.258612839</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-5128552.57498084</t>
+          <t>-9404152.255840585</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1723.405</t>
+          <t>815.443</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-77.34</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,66 +5656,66 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>815</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>35.21</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-2.17</v>
+        <v>-0.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>-3.85</v>
+        <v>-2.32</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-19.75</t>
+          <t>-20.29</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.66</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>41.25</v>
+        <v>40.69</v>
       </c>
       <c r="AN13" t="n">
-        <v>51.4</v>
+        <v>51.05</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>53.89</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>-3.79</v>
+        <v>-3.58</v>
       </c>
       <c r="AR13" t="n">
-        <v>-4.32</v>
+        <v>-4.17</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-143.34</t>
+          <t>-141.86</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>817062813.061702</t>
+          <t>815973425.8194051</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>67561114.0</t>
+          <t>31970280.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>57030358.8</v>
+        <v>55431253.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>58864658.8</t>
+          <t>55033166.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>105014037.38</v>
+        <v>104370124.22</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1834300</t>
+          <t>398087</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-8360252.191026547</t>
+          <t>-9043079.47071227</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-11490512.01097466</t>
+          <t>-12798629.50898375</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>67561114.0</t>
+          <t>31970280.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-35.33</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5835,22 +5835,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1402.498</t>
+          <t>1723.405</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5972,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-13.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-76.96</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,66 +6078,66 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>815</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>66.04</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>70.24</t>
+          <t>56.73</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>1.41</v>
+        <v>-2.17</v>
       </c>
       <c r="AI14" t="n">
-        <v>-5.63</v>
+        <v>-3.85</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-19.75</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.64</t>
+          <t>39.66</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>42</v>
+        <v>41.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>51.77</v>
+        <v>51.4</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>54.39</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>-3.92</v>
+        <v>-3.79</v>
       </c>
       <c r="AR14" t="n">
-        <v>-4.45</v>
+        <v>-4.32</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-144.66</t>
+          <t>-143.34</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>817062813.061702</t>
+          <t>815973425.8194051</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>56866738.0</t>
+          <t>67561114.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>52170587</v>
+        <v>57030358.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>60387674.3</t>
+          <t>58864658.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>104657046.58</v>
+        <v>105014037.38</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-8217087</t>
+          <t>-1834300</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-7791114.041945071</t>
+          <t>-8360252.191026547</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-13024700.9419983</t>
+          <t>-11490512.01097466</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>56866738.0</t>
+          <t>67561114.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-35.33</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6257,22 +6257,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6322,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2004.052</t>
+          <t>1402.498</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-13.61</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-76.45</t>
+          <t>-76.96</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6500,66 +6500,66 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>815</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.04</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>70.24</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>4.16</v>
+        <v>1.41</v>
       </c>
       <c r="AI15" t="n">
-        <v>-7.83</v>
+        <v>-5.63</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.45999999999999</t>
+          <t>39.64</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>42.81</v>
+        <v>42</v>
       </c>
       <c r="AN15" t="n">
-        <v>52.12</v>
+        <v>51.77</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>-4.18</v>
+        <v>-3.92</v>
       </c>
       <c r="AR15" t="n">
-        <v>-4.58</v>
+        <v>-4.45</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-145.99</t>
+          <t>-144.66</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>817062813.061702</t>
+          <t>815973425.8194051</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>81179444.0</t>
+          <t>56866738.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>52542179</v>
+        <v>52170587</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>70182172.1</t>
+          <t>60387674.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>104757662.2</v>
+        <v>104657046.58</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-17639993</t>
+          <t>-8217087</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-6839552.787389938</t>
+          <t>-7791114.041945071</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-13605405.52410358</t>
+          <t>-13024700.9419983</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>81179444.0</t>
+          <t>56866738.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-31.50</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6679,22 +6679,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6744,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1008.964</t>
+          <t>2004.052</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-38.43</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-77.59</t>
+          <t>-76.45</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>12.16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6922,66 +6922,66 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>815</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>-0.5600000000000001</v>
+        <v>4.16</v>
       </c>
       <c r="AI16" t="n">
-        <v>-9.869999999999999</v>
+        <v>-7.83</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-16.88</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.45999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>43.62</v>
+        <v>42.81</v>
       </c>
       <c r="AN16" t="n">
-        <v>52.48</v>
+        <v>52.12</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>-4.53</v>
+        <v>-4.18</v>
       </c>
       <c r="AR16" t="n">
-        <v>-4.68</v>
+        <v>-4.58</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-147.00</t>
+          <t>-145.99</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>817062813.061702</t>
+          <t>815973425.8194051</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39578693.0</t>
+          <t>81179444.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>45879187.4</v>
+        <v>52542179</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>74516116.7</t>
+          <t>70182172.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>104984462.56</v>
+        <v>104757662.2</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-28636929</t>
+          <t>-17639993</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5609397.744351093</t>
+          <t>-6839552.787389938</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-16554008.94410741</t>
+          <t>-13605405.52410358</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>39578693.0</t>
+          <t>81179444.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-34.83</t>
+          <t>-31.50</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7101,22 +7101,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7171,17 +7171,17 @@
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7203,7 +7203,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1019.0</t>
+          <t>1008.964</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-36.24</t>
+          <t>-38.43</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7344,12 +7344,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>815</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7359,51 +7359,51 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>-1.19</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AI17" t="n">
-        <v>-11.16</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.88</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>44.54</v>
+        <v>43.62</v>
       </c>
       <c r="AN17" t="n">
-        <v>52.9</v>
+        <v>52.48</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>56.44</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>-4.72</v>
+        <v>-4.53</v>
       </c>
       <c r="AR17" t="n">
-        <v>-4.72</v>
+        <v>-4.68</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-147.37</t>
+          <t>-147.00</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>817062813.061702</t>
+          <t>815973425.8194051</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>39965805.0</t>
+          <t>39578693.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>54635078.8</v>
+        <v>45879187.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>85690900.6</t>
+          <t>74516116.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>108163023.8</v>
+        <v>104984462.56</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-31055821</t>
+          <t>-28636929</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3619468.435304489</t>
+          <t>-5609397.744351093</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-15717861.61753762</t>
+          <t>-16554008.94410741</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>39965805.0</t>
+          <t>39578693.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1116.892</t>
+          <t>1019.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7660,17 +7660,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-53.69</t>
+          <t>-36.24</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-77.82</t>
+          <t>-77.59</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7766,63 +7766,63 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>815</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>45.04</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>-1.88</v>
+        <v>-1.19</v>
       </c>
       <c r="AI18" t="n">
-        <v>-13.37</v>
+        <v>-11.16</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-14.54</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>45.52</v>
+        <v>44.54</v>
       </c>
       <c r="AN18" t="n">
-        <v>53.27</v>
+        <v>52.9</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>56.99</t>
+          <t>56.44</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>-4.89</v>
+        <v>-4.72</v>
       </c>
       <c r="AR18" t="n">
         <v>-4.72</v>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-147.36</t>
+          <t>-147.37</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>817062813.061702</t>
+          <t>815973425.8194051</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>43262255.0</t>
+          <t>39965805.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>60698958.8</v>
+        <v>54635078.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>131072655.7</t>
+          <t>85690900.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>108812256.18</v>
+        <v>108163023.8</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-70373696</t>
+          <t>-31055821</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-1419760.583989375</t>
+          <t>-3619468.435304489</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-14003489.52181157</t>
+          <t>-15717861.61753762</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>43262255.0</t>
+          <t>39965805.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-34.83</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7945,22 +7945,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8010,22 +8010,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1488.337</t>
+          <t>1116.892</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-48.94</t>
+          <t>-53.69</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.82</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8188,66 +8188,66 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>815</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>48.49</t>
+          <t>45.04</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>-0.03</v>
+        <v>-1.88</v>
       </c>
       <c r="AI19" t="n">
-        <v>-15.58</v>
+        <v>-13.37</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-13.13</t>
+          <t>-14.54</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>46.56</v>
+        <v>45.52</v>
       </c>
       <c r="AN19" t="n">
-        <v>53.6</v>
+        <v>53.27</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>56.99</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>-4.99</v>
+        <v>-4.89</v>
       </c>
       <c r="AR19" t="n">
-        <v>-4.67</v>
+        <v>-4.72</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-146.93</t>
+          <t>-147.36</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>817062813.061702</t>
+          <t>815973425.8194051</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>58724698.0</t>
+          <t>43262255.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>68604761.59999999</v>
+        <v>60698958.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>134363485.4</t>
+          <t>131072655.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>108539531.38</v>
+        <v>108812256.18</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-65758723</t>
+          <t>-70373696</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>868190.1319782983</t>
+          <t>-1419760.583989375</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-11407452.9735668</t>
+          <t>-14003489.52181157</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>58724698.0</t>
+          <t>43262255.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8377,12 +8377,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8432,22 +8432,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1193.144</t>
+          <t>1488.337</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-34.10</t>
+          <t>-48.94</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8610,66 +8610,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>815</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>48.49</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>2.51</v>
+        <v>-0.03</v>
       </c>
       <c r="AI20" t="n">
-        <v>-17.28</v>
+        <v>-15.58</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-11.66</t>
+          <t>-13.13</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>39.41</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>47.64</v>
+        <v>46.56</v>
       </c>
       <c r="AN20" t="n">
-        <v>53.93</v>
+        <v>53.6</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>-5.11</v>
+        <v>-4.99</v>
       </c>
       <c r="AR20" t="n">
-        <v>-4.59</v>
+        <v>-4.67</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-146.12</t>
+          <t>-146.93</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>817062813.061702</t>
+          <t>815973425.8194051</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>47864486.0</t>
+          <t>58724698.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>87822165.2</v>
+        <v>68604761.59999999</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>133257287.4</t>
+          <t>134363485.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>108220642.86</v>
+        <v>108539531.38</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-45435122</t>
+          <t>-65758723</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>3100125.242077407</t>
+          <t>868190.1319782983</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-8948110.61987549</t>
+          <t>-11407452.9735668</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>47864486.0</t>
+          <t>58724698.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8789,22 +8789,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8854,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2106.06</t>
+          <t>1193.144</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-27.07</t>
+          <t>-34.10</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-76.88</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,66 +9032,66 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>815</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>37.27</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>3.44</v>
+        <v>2.51</v>
       </c>
       <c r="AI21" t="n">
-        <v>-19.77</v>
+        <v>-17.28</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-10.35</t>
+          <t>-11.66</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>39.01000000000001</t>
+          <t>39.41</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>48.62</v>
+        <v>47.64</v>
       </c>
       <c r="AN21" t="n">
-        <v>54.24</v>
+        <v>53.93</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>58.61</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-18.89</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>-5.31</v>
+        <v>-5.11</v>
       </c>
       <c r="AR21" t="n">
-        <v>-4.46</v>
+        <v>-4.59</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-144.82</t>
+          <t>-146.12</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>817062813.061702</t>
+          <t>815973425.8194051</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>103153046</v>
+        <v>87822165.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>141449078.375</t>
+          <t>133257287.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>108192095.52</v>
+        <v>108220642.86</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-38296032</t>
+          <t>-45435122</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>5290713.580614299</t>
+          <t>3100125.242077407</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3951594.87817803</t>
+          <t>-8948110.61987549</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9211,12 +9211,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1860.309</t>
+          <t>2106.06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-27.07</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-77.97</t>
+          <t>-76.88</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>12.77</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9454,66 +9454,66 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>815</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>-0.93</v>
+        <v>3.44</v>
       </c>
       <c r="AI22" t="n">
-        <v>-21.77</v>
+        <v>-19.77</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-10.35</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>39.01000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>49.61</v>
+        <v>48.62</v>
       </c>
       <c r="AN22" t="n">
-        <v>54.55</v>
+        <v>54.24</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>58.61</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-28.62</t>
+          <t>-18.89</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>-5.47</v>
+        <v>-5.31</v>
       </c>
       <c r="AR22" t="n">
-        <v>-4.25</v>
+        <v>-4.46</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-142.70</t>
+          <t>-144.82</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>817062813.061702</t>
+          <t>815973425.8194051</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>70285205.0</t>
+          <t>83358150.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>116746722.4</v>
+        <v>103153046</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>150434379.975</t>
+          <t>141449078.375</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>108165555.1</v>
+        <v>108192095.52</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-33687657</t>
+          <t>-38296032</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>6971133.300394721</t>
+          <t>5290713.580614299</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-475479.4301038831</t>
+          <t>-3951594.87817803</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>70285205.0</t>
+          <t>83358150.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-35.92</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9698,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
+          <t>40.35</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>38.5</t>
         </is>
       </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>37.15</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2129.764</t>
+          <t>1860.309</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9770,17 +9770,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-77.97</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9876,66 +9876,66 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>815</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>-3.43</v>
+        <v>-0.93</v>
       </c>
       <c r="AI23" t="n">
-        <v>-22.16</v>
+        <v>-21.77</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.62</v>
+        <v>49.61</v>
       </c>
       <c r="AN23" t="n">
-        <v>54.92</v>
+        <v>54.55</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-36.90</t>
+          <t>-28.62</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>-5.41</v>
+        <v>-5.47</v>
       </c>
       <c r="AR23" t="n">
-        <v>-3.95</v>
+        <v>-4.25</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-139.64</t>
+          <t>-142.70</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>817062813.061702</t>
+          <t>815973425.8194051</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>82791269.0</t>
+          <t>70285205.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>201446352.6</v>
+        <v>116746722.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>159445296.375</t>
+          <t>150434379.975</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>108301709.3</v>
+        <v>108165555.1</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>42001056</t>
+          <t>-33687657</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>8325062.887758104</t>
+          <t>6971133.300394721</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>5908053.868220031</t>
+          <t>-475479.4301038831</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>82791269.0</t>
+          <t>70285205.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-36.58</t>
+          <t>-35.92</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>300.074</t>
+          <t>385.635</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-20.04</t>
+          <t>-18.75</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10277,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10298,66 +10298,66 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>386</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>-0.34</v>
+        <v>-0.27</v>
       </c>
       <c r="AI24" t="n">
-        <v>-4.74</v>
+        <v>-3.55</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>27.39</v>
+        <v>27.03</v>
       </c>
       <c r="AN24" t="n">
-        <v>32.64</v>
+        <v>32.46</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>-2.11</v>
+        <v>-2</v>
       </c>
       <c r="AR24" t="n">
-        <v>-2.35</v>
+        <v>-2.28</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-156.14</t>
+          <t>-154.48</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10376,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>231831780.7754957</t>
+          <t>231525020.8429986</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>7827955.0</t>
+          <t>9968339.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>9442320.800000001</v>
+        <v>9257823.199999999</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>11809321.3</t>
+          <t>11393836.2</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>48370630.4</v>
+        <v>47719309.62</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-2367000</t>
+          <t>-2136013</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-5565162.609483169</t>
+          <t>-5709385.359917476</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-7024278.613318738</t>
+          <t>-6502610.487306161</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>7827955.0</t>
+          <t>9968339.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
@@ -10542,17 +10542,17 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>345.581</t>
+          <t>300.074</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10614,17 +10614,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-20.52</t>
+          <t>-20.04</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-46.52</t>
+          <t>-46.72</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10699,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10720,66 +10720,66 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>386</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>0.31</v>
+        <v>-0.34</v>
       </c>
       <c r="AI25" t="n">
-        <v>-6.34</v>
+        <v>-4.74</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-15.31</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>27.78</v>
+        <v>27.39</v>
       </c>
       <c r="AN25" t="n">
-        <v>32.8</v>
+        <v>32.64</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>-2.21</v>
+        <v>-2.11</v>
       </c>
       <c r="AR25" t="n">
-        <v>-2.41</v>
+        <v>-2.35</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-157.58</t>
+          <t>-156.14</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10798,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>231831780.7754957</t>
+          <t>231525020.8429986</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>9099621.0</t>
+          <t>7827955.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>10056805.4</v>
+        <v>9442320.800000001</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>12653110.1</t>
+          <t>11809321.3</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>48733537.5</v>
+        <v>48370630.4</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-2596304</t>
+          <t>-2367000</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-5299868.790603975</t>
+          <t>-5565162.609483169</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-7289324.842861038</t>
+          <t>-7024278.613318738</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>9099621.0</t>
+          <t>7827955.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-31.13</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
@@ -10964,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>412.175</t>
+          <t>345.581</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11036,17 +11036,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-20.52</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-46.21</t>
+          <t>-46.52</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11121,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11142,38 +11142,38 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>386</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="AI26" t="n">
-        <v>-7.67</v>
+        <v>-6.34</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-15.31</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -11182,26 +11182,26 @@
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>28.18</v>
+        <v>27.78</v>
       </c>
       <c r="AN26" t="n">
-        <v>32.97</v>
+        <v>32.8</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-2.32</v>
+        <v>-2.21</v>
       </c>
       <c r="AR26" t="n">
-        <v>-2.46</v>
+        <v>-2.41</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-158.77</t>
+          <t>-157.58</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11220,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>231831780.7754957</t>
+          <t>231525020.8429986</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>10874743.0</t>
+          <t>9099621.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>10677592.6</v>
+        <v>10056805.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>15303859.3</t>
+          <t>12653110.1</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>48839305.12</v>
+        <v>48733537.5</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-4626266</t>
+          <t>-2596304</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-4938149.508375417</t>
+          <t>-5299868.790603975</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-7543879.212104999</t>
+          <t>-7289324.842861038</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>10874743.0</t>
+          <t>9099621.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-30.46</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
@@ -11386,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>324.726</t>
+          <t>412.175</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11458,17 +11458,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-35.94</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-46.72</t>
+          <t>-46.21</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11543,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11564,66 +11564,66 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>386</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>51.61</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>-0.34</v>
+        <v>0.88</v>
       </c>
       <c r="AI27" t="n">
-        <v>-8.76</v>
+        <v>-7.67</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>28.6</v>
+        <v>28.18</v>
       </c>
       <c r="AN27" t="n">
-        <v>33.14</v>
+        <v>32.97</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.51</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-2.45</v>
+        <v>-2.32</v>
       </c>
       <c r="AR27" t="n">
-        <v>-2.49</v>
+        <v>-2.46</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-159.58</t>
+          <t>-158.77</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11642,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>231831780.7754957</t>
+          <t>231525020.8429986</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>8518458.0</t>
+          <t>10874743.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>11755155.8</v>
+        <v>10677592.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>18350491.6</t>
+          <t>15303859.3</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>48982652.58</v>
+        <v>48839305.12</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-6595335</t>
+          <t>-4626266</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-4464380.471333675</t>
+          <t>-4938149.508375417</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-7828295.69630691</t>
+          <t>-7543879.212104999</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>8518458.0</t>
+          <t>10874743.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-31.13</t>
+          <t>-30.46</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11845,7 +11845,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>418.856</t>
+          <t>324.726</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11880,17 +11880,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-43.13</t>
+          <t>-35.94</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-46.52</t>
+          <t>-46.72</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11986,66 +11986,66 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>386</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>-0.72</v>
+        <v>-0.34</v>
       </c>
       <c r="AI28" t="n">
-        <v>-9.43</v>
+        <v>-8.76</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-12.88</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>26.29</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>29.03</v>
+        <v>28.6</v>
       </c>
       <c r="AN28" t="n">
-        <v>33.32</v>
+        <v>33.14</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>-2.54</v>
+        <v>-2.45</v>
       </c>
       <c r="AR28" t="n">
-        <v>-2.51</v>
+        <v>-2.49</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-159.87</t>
+          <t>-159.58</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12064,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>231831780.7754957</t>
+          <t>231525020.8429986</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>10890827.0</t>
+          <t>8518458.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>13529849.2</v>
+        <v>11755155.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>23791154.3</t>
+          <t>18350491.6</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>49422294.62</v>
+        <v>48982652.58</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-10261305</t>
+          <t>-6595335</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-3852759.521338541</t>
+          <t>-4464380.471333675</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-7702563.863155823</t>
+          <t>-7828295.69630691</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>10890827.0</t>
+          <t>8518458.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-31.13</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12165,17 +12165,17 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
@@ -12230,22 +12230,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
+          <t>26.2</t>
+        </is>
+      </c>
+      <c r="CE28" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="CF28" t="inlineStr">
+        <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="CE28" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="CF28" t="inlineStr">
-        <is>
-          <t>25.65</t>
-        </is>
-      </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>422.572</t>
+          <t>418.856</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12302,17 +12302,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-70.11</t>
+          <t>-43.13</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-47.44</t>
+          <t>-46.52</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12387,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12408,66 +12408,66 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>386</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>45.97</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>-2.47</v>
+        <v>-0.72</v>
       </c>
       <c r="AI29" t="n">
-        <v>-10.88</v>
+        <v>-9.43</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-12.88</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.29</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>29.51</v>
+        <v>29.03</v>
       </c>
       <c r="AN29" t="n">
-        <v>33.48</v>
+        <v>33.32</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>-2.64</v>
+        <v>-2.54</v>
       </c>
       <c r="AR29" t="n">
-        <v>-2.5</v>
+        <v>-2.51</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-159.66</t>
+          <t>-159.87</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12486,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>231831780.7754957</t>
+          <t>231525020.8429986</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>10900378.0</t>
+          <t>10890827.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>14176321.8</v>
+        <v>13529849.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>47420905.2</t>
+          <t>23791154.3</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>49617005.26</v>
+        <v>49422294.62</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-33244583</t>
+          <t>-10261305</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-3152795.095553581</t>
+          <t>-3852759.521338541</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-7502037.784970127</t>
+          <t>-7702563.863155823</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>10900378.0</t>
+          <t>10890827.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-32.05</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12587,17 +12587,17 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
@@ -12652,22 +12652,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>465.71</t>
+          <t>422.572</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12724,17 +12724,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-69.34</t>
+          <t>-70.11</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-46.52</t>
+          <t>-47.44</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12809,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12830,66 +12830,66 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>386</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>45.97</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>-0.61</v>
+        <v>-2.47</v>
       </c>
       <c r="AI30" t="n">
-        <v>-12.66</v>
+        <v>-10.88</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>30.07</v>
+        <v>29.51</v>
       </c>
       <c r="AN30" t="n">
-        <v>33.64</v>
+        <v>33.48</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>-2.68</v>
+        <v>-2.64</v>
       </c>
       <c r="AR30" t="n">
-        <v>-2.46</v>
+        <v>-2.5</v>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-158.82</t>
+          <t>-159.66</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12908,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>231831780.7754957</t>
+          <t>231525020.8429986</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>12203557.0</t>
+          <t>10900378.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>15249414.8</v>
+        <v>14176321.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>49734645.5</t>
+          <t>47420905.2</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>49796767.5</v>
+        <v>49617005.26</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-34485230</t>
+          <t>-33244583</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-2362023.697477845</t>
+          <t>-3152795.095553581</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-6948665.359527342</t>
+          <t>-7502037.784970127</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>12203557.0</t>
+          <t>10900378.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-32.05</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
@@ -13074,22 +13074,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13121,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>612.432</t>
+          <t>465.71</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13146,17 +13146,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-60.87</t>
+          <t>-69.34</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-45.49</t>
+          <t>-46.52</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13231,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13252,66 +13252,66 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>386</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>70.27</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>1.84</v>
+        <v>-0.61</v>
       </c>
       <c r="AI31" t="n">
-        <v>-14.68</v>
+        <v>-12.66</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>30.62</v>
+        <v>30.07</v>
       </c>
       <c r="AN31" t="n">
-        <v>33.79</v>
+        <v>33.64</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>-2.73</v>
+        <v>-2.68</v>
       </c>
       <c r="AR31" t="n">
-        <v>-2.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-157.54</t>
+          <t>-158.82</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13330,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>231831780.7754957</t>
+          <t>231525020.8429986</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>16262559.0</t>
+          <t>12203557.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>19930126</v>
+        <v>15249414.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>50938580.6</t>
+          <t>49734645.5</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>50167990.62</v>
+        <v>49796767.5</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-31008454</t>
+          <t>-34485230</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-1528088.849832482</t>
+          <t>-2362023.697477845</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-6049593.024625957</t>
+          <t>-6948665.359527342</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>16262559.0</t>
+          <t>12203557.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-29.54</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13431,17 +13431,17 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
@@ -13496,22 +13496,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>649.691</t>
+          <t>612.432</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13568,17 +13568,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-52.69</t>
+          <t>-60.87</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-44.67</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13674,66 +13674,66 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>386</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>70.27</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>4.41</v>
+        <v>1.84</v>
       </c>
       <c r="AI32" t="n">
-        <v>-16.92</v>
+        <v>-14.68</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-9.4</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>31.12</v>
+        <v>30.62</v>
       </c>
       <c r="AN32" t="n">
-        <v>33.95</v>
+        <v>33.79</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>-2.81</v>
+        <v>-2.73</v>
       </c>
       <c r="AR32" t="n">
-        <v>-2.33</v>
+        <v>-2.41</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-155.61</t>
+          <t>-157.54</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13752,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>231831780.7754957</t>
+          <t>231525020.8429986</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>24945827.4</v>
+        <v>19930126</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>52732533.125</t>
+          <t>50938580.6</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>50214218.22</v>
+        <v>50167990.62</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-27786705</t>
+          <t>-31008454</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-705997.1816882136</t>
+          <t>-1528088.849832482</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-4984040.152458765</t>
+          <t>-6049593.024625957</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-28.48</t>
+          <t>-29.54</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
@@ -13918,22 +13918,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>547.074</t>
+          <t>649.691</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-35.13</t>
+          <t>-52.69</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-46.41</t>
+          <t>-44.67</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14075,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14096,66 +14096,66 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>386</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>1.91</v>
+        <v>4.41</v>
       </c>
       <c r="AI33" t="n">
-        <v>-18.87</v>
+        <v>-16.92</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>25.66</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>31.63</v>
+        <v>31.12</v>
       </c>
       <c r="AN33" t="n">
-        <v>34.09</v>
+        <v>33.95</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-32.22</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>-2.92</v>
+        <v>-2.81</v>
       </c>
       <c r="AR33" t="n">
-        <v>-2.21</v>
+        <v>-2.33</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-152.71</t>
+          <t>-155.61</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14174,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>231831780.7754957</t>
+          <t>231525020.8429986</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>14123190.0</t>
+          <t>17391925.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>34052459.4</v>
+        <v>24945827.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>52493236.225</t>
+          <t>52732533.125</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>50697236.3</v>
+        <v>50214218.22</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-18440776</t>
+          <t>-27786705</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>71828.81299734116</t>
+          <t>-705997.1816882136</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-3404823.829632118</t>
+          <t>-4984040.152458765</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>14123190.0</t>
+          <t>17391925.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-28.48</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
@@ -14340,22 +14340,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>642.086</t>
+          <t>547.074</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14412,17 +14412,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>-35.13</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-47.85</t>
+          <t>-46.41</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14497,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14518,66 +14518,66 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>386</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>-0.93</v>
+        <v>1.91</v>
       </c>
       <c r="AI34" t="n">
-        <v>-20.16</v>
+        <v>-18.87</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>25.66</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>32.18</v>
+        <v>31.63</v>
       </c>
       <c r="AN34" t="n">
-        <v>34.27</v>
+        <v>34.09</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>-32.22</t>
         </is>
       </c>
       <c r="AQ34" t="n">
         <v>-2.92</v>
       </c>
       <c r="AR34" t="n">
-        <v>-2.03</v>
+        <v>-2.21</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-148.47</t>
+          <t>-152.71</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14596,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>231831780.7754957</t>
+          <t>231525020.8429986</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>16265843.0</t>
+          <t>14123190.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>80665488.59999999</v>
+        <v>34052459.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>55106397.425</t>
+          <t>52493236.225</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>50819476.86</v>
+        <v>50697236.3</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>25559091</t>
+          <t>-18440776</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>703947.4752936066</t>
+          <t>71828.81299734116</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-676978.0531071872</t>
+          <t>-3404823.829632118</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>16265843.0</t>
+          <t>14123190.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-32.58</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/風機維護.xlsx
+++ b/Result/checksun_type/風機維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>883.816</t>
+          <t>1030.282</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.6</v>
+        <v>-0.36</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.36</v>
+        <v>-0.15</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.48</t>
+          <t>-9.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>41.5</v>
+        <v>41.31</v>
       </c>
       <c r="AN2" t="n">
-        <v>45.85</v>
+        <v>45.73</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.37</v>
+        <v>-1.31</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.57</v>
+        <v>-1.52</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-168.90</t>
+          <t>-166.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>155477034.25811</t>
+          <t>155347142.8077465</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>36403205.0</t>
+          <t>42169403.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>31223284</v>
+        <v>35173544</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>33395418.0</t>
+          <t>35554392.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>80582619.42</v>
+        <v>80881526.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2172134</t>
+          <t>-380848</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-10135575.66043107</t>
+          <t>-9901093.45823767</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-10202833.53182393</t>
+          <t>-8611441.346173972</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>36403205.0</t>
+          <t>42169403.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>869.687</t>
+          <t>883.816</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,38 +1436,38 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="AH3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AI3" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AI3" t="n">
-        <v>-1.27</v>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.48</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1476,26 +1476,26 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>41.88</v>
+        <v>41.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>45.96</v>
+        <v>45.85</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.43</v>
+        <v>-1.37</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.62</v>
+        <v>-1.57</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-171.08</t>
+          <t>-168.90</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>155477034.25811</t>
+          <t>155347142.8077465</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>35987726.0</t>
+          <t>36403205.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>30143744</v>
+        <v>31223284</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>32888445.3</t>
+          <t>33395418.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>80758886.90000001</v>
+        <v>80582619.42</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2744701</t>
+          <t>-2172134</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-10123346.95654146</t>
+          <t>-10135575.66043107</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-11494057.09947302</t>
+          <t>-10202833.53182393</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>35987726.0</t>
+          <t>36403205.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>697.346</t>
+          <t>869.687</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-16.04</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.58</v>
+        <v>-0.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2.23</v>
+        <v>-1.27</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>42.25</v>
+        <v>41.88</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.07</v>
+        <v>45.96</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.5</v>
+        <v>-1.43</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.66</v>
+        <v>-1.62</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-173.14</t>
+          <t>-171.08</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>155477034.25811</t>
+          <t>155347142.8077465</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>28887127.0</t>
+          <t>35987726.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>27672720.4</v>
+        <v>30143744</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>32958978.8</t>
+          <t>32888445.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>80464167.98</v>
+        <v>80758886.90000001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5286258</t>
+          <t>-2744701</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-9874126.9305539</t>
+          <t>-10123346.95654146</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-12883644.54970483</t>
+          <t>-11494057.09947302</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>28887127.0</t>
+          <t>35987726.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>784.322</t>
+          <t>697.346</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-16.04</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.23</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.22</v>
+        <v>0.58</v>
       </c>
       <c r="AI5" t="n">
-        <v>-3.36</v>
+        <v>-2.23</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>42.64</v>
+        <v>42.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.18</v>
+        <v>46.07</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.71</v>
+        <v>-1.66</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-174.98</t>
+          <t>-173.14</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>155477034.25811</t>
+          <t>155347142.8077465</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>32420259.0</t>
+          <t>28887127.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>33017021.4</v>
+        <v>27672720.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>35338581.4</t>
+          <t>32958978.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>80798522.31999999</v>
+        <v>80464167.98</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2321560</t>
+          <t>-5286258</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-9326941.908890095</t>
+          <t>-9874126.9305539</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-13647860.85183223</t>
+          <t>-12883644.54970483</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>32420259.0</t>
+          <t>28887127.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-8.28</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>540.472</t>
+          <t>784.322</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.60</t>
+          <t>-14.23</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.85</v>
+        <v>0.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>-4.19</v>
+        <v>-3.36</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>43.06</v>
+        <v>42.64</v>
       </c>
       <c r="AN6" t="n">
-        <v>46.27</v>
+        <v>46.18</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.68</v>
+        <v>-1.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.73</v>
+        <v>-1.71</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-176.17</t>
+          <t>-174.98</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>155477034.25811</t>
+          <t>155347142.8077465</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>22418103.0</t>
+          <t>32420259.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>35935241</v>
+        <v>33017021.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>36654566.2</t>
+          <t>35338581.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>80677329.12</v>
+        <v>80798522.31999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-719325</t>
+          <t>-2321560</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8541320.282900617</t>
+          <t>-9326941.908890095</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-14630724.68159164</t>
+          <t>-13647860.85183223</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>22418103.0</t>
+          <t>32420259.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>756.121</t>
+          <t>540.472</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-13.60</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.41</v>
+        <v>0.85</v>
       </c>
       <c r="AI7" t="n">
-        <v>-5.03</v>
+        <v>-4.19</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.25</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>43.46</v>
+        <v>43.06</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.36</v>
+        <v>46.27</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.78</v>
+        <v>-1.68</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.75</v>
+        <v>-1.73</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-176.81</t>
+          <t>-176.17</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>155477034.25811</t>
+          <t>155347142.8077465</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>31005505.0</t>
+          <t>22418103.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>35567552</v>
+        <v>35935241</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>40983034.9</t>
+          <t>36654566.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>81047113.98</v>
+        <v>80677329.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5415482</t>
+          <t>-719325</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-7434155.846774974</t>
+          <t>-8541320.282900617</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-14440630.41404826</t>
+          <t>-14630724.68159164</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>31005505.0</t>
+          <t>22418103.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>574.591</t>
+          <t>756.121</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.74</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.85</v>
+        <v>-0.41</v>
       </c>
       <c r="AI8" t="n">
-        <v>-5.74</v>
+        <v>-5.03</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>43.87</v>
+        <v>43.46</v>
       </c>
       <c r="AN8" t="n">
-        <v>46.46</v>
+        <v>46.36</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.62</t>
+          <t>46.57</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.84</v>
+        <v>-1.78</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.74</v>
+        <v>-1.75</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-176.43</t>
+          <t>-176.81</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>155477034.25811</t>
+          <t>155347142.8077465</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>23632608.0</t>
+          <t>31005505.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>35633146.6</v>
+        <v>35567552</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>46120346.0</t>
+          <t>40983034.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>81185268.44</v>
+        <v>81047113.98</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-10487199</t>
+          <t>-5415482</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6160251.379998012</t>
+          <t>-7434155.846774974</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-14573409.15991313</t>
+          <t>-14440630.41404826</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>23632608.0</t>
+          <t>31005505.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1347.469</t>
+          <t>574.591</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-39.94</t>
+          <t>-22.74</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.75</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,38 +3968,38 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.73</v>
+        <v>-0.85</v>
       </c>
       <c r="AI9" t="n">
-        <v>-6.6</v>
+        <v>-5.74</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4008,26 +4008,26 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>44.27</v>
+        <v>43.87</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.56</v>
+        <v>46.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.62</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.88</v>
+        <v>-1.84</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.71</v>
+        <v>-1.74</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-175.31</t>
+          <t>-176.43</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>155477034.25811</t>
+          <t>155347142.8077465</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>55608632.0</t>
+          <t>23632608.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>38245237.2</v>
+        <v>35633146.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>63682089.3</t>
+          <t>46120346.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>81578099.64</v>
+        <v>81185268.44</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-25436852</t>
+          <t>-10487199</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4630586.329104355</t>
+          <t>-6160251.379998012</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-13452660.9340089</t>
+          <t>-14573409.15991313</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>55608632.0</t>
+          <t>23632608.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1130.918</t>
+          <t>1347.469</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-49.63</t>
+          <t>-39.94</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.75</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>78.27</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.29</v>
+        <v>-0.73</v>
       </c>
       <c r="AI10" t="n">
-        <v>-7.32</v>
+        <v>-6.6</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>44.65</v>
+        <v>44.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.66</v>
+        <v>46.56</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.72</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-14.01</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.91</v>
+        <v>-1.88</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.67</v>
+        <v>-1.71</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-173.49</t>
+          <t>-175.31</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>155477034.25811</t>
+          <t>155347142.8077465</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>37660141.4</v>
+        <v>38245237.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>74772185.0</t>
+          <t>63682089.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>81458753.88</v>
+        <v>81578099.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-37112043</t>
+          <t>-25436852</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3026572.764576255</t>
+          <t>-4630586.329104355</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-14797142.43507398</t>
+          <t>-13452660.9340089</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>495.163</t>
+          <t>1130.918</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-59.35</t>
+          <t>-49.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>78.27</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.97</v>
+        <v>0.29</v>
       </c>
       <c r="AI11" t="n">
-        <v>-8.199999999999999</v>
+        <v>-7.32</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>44.99</v>
+        <v>44.65</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.76</v>
+        <v>46.66</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-14.01</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.96</v>
+        <v>-1.91</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.61</v>
+        <v>-1.67</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-170.91</t>
+          <t>-173.49</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>155477034.25811</t>
+          <t>155347142.8077465</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>37373891.4</v>
+        <v>37660141.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>91945361.2</t>
+          <t>74772185.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>81397712.23999999</v>
+        <v>81458753.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-54571469</t>
+          <t>-37112043</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-886469.1881221232</t>
+          <t>-3026572.764576255</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-15268224.31391429</t>
+          <t>-14797142.43507398</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>754.379</t>
+          <t>495.163</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-64.70</t>
+          <t>-59.35</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="AI12" t="n">
-        <v>-8.98</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>45.3</v>
+        <v>44.99</v>
       </c>
       <c r="AN12" t="n">
-        <v>46.87</v>
+        <v>46.76</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.02</v>
+        <v>-1.96</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.53</v>
+        <v>-1.61</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-167.12</t>
+          <t>-170.91</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>155477034.25811</t>
+          <t>155347142.8077465</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>46398517.8</v>
+        <v>37373891.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>131458358.1</t>
+          <t>91945361.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>82367727.08</v>
+        <v>81397712.23999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-85059840</t>
+          <t>-54571469</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1728395.380203726</t>
+          <t>-886469.1881221232</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-12563936.95104639</t>
+          <t>-15268224.31391429</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>797.983</t>
+          <t>1826.022</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-77.74</t>
+          <t>-78.45</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,66 +5656,66 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-2.14</v>
+        <v>-3.59</v>
       </c>
       <c r="AI13" t="n">
-        <v>-1.21</v>
+        <v>-1.55</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-20.71</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>40.18</v>
+        <v>39.62</v>
       </c>
       <c r="AN13" t="n">
-        <v>50.68</v>
+        <v>50.33</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.48</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>-3.43</v>
+        <v>-3.38</v>
       </c>
       <c r="AR13" t="n">
-        <v>-4.02</v>
+        <v>-3.89</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-140.38</t>
+          <t>-139.09</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>814885812.5495049</t>
+          <t>813881121.3728814</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>31353896.0</t>
+          <t>69042973.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>53786294.4</v>
+        <v>51359000.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>49832740.9</t>
+          <t>51950589.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>104069203.72</v>
+        <v>104079766.08</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3953553</t>
+          <t>-591589</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-9719617.216735845</t>
+          <t>-9874636.320620501</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-13440574.81986551</t>
+          <t>-10727241.39198611</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>31353896.0</t>
+          <t>69042973.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-35.25</t>
+          <t>-37.33</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>815.443</t>
+          <t>797.983</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5972,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-77.34</t>
+          <t>-77.74</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,66 +6078,66 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>35.21</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>-0.5</v>
+        <v>-2.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>-2.32</v>
+        <v>-1.21</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-20.29</t>
+          <t>-20.71</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>40.69</v>
+        <v>40.18</v>
       </c>
       <c r="AN14" t="n">
-        <v>51.05</v>
+        <v>50.68</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>53.48</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>-3.58</v>
+        <v>-3.43</v>
       </c>
       <c r="AR14" t="n">
-        <v>-4.17</v>
+        <v>-4.02</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-141.86</t>
+          <t>-140.38</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>814885812.5495049</t>
+          <t>813881121.3728814</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31970280.0</t>
+          <t>31353896.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>55431253.8</v>
+        <v>53786294.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>55033166.3</t>
+          <t>49832740.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>104370124.22</v>
+        <v>104069203.72</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>398087</t>
+          <t>3953553</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-9043079.47071227</t>
+          <t>-9719617.216735845</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-12798629.50898375</t>
+          <t>-13440574.81986551</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>31970280.0</t>
+          <t>31353896.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-35.25</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6322,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1723.405</t>
+          <t>815.443</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-77.34</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6500,66 +6500,66 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>35.21</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>-2.17</v>
+        <v>-0.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>-3.85</v>
+        <v>-2.32</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-19.75</t>
+          <t>-20.29</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.66</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>41.25</v>
+        <v>40.69</v>
       </c>
       <c r="AN15" t="n">
-        <v>51.4</v>
+        <v>51.05</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>53.89</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>-3.79</v>
+        <v>-3.58</v>
       </c>
       <c r="AR15" t="n">
-        <v>-4.32</v>
+        <v>-4.17</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-143.34</t>
+          <t>-141.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>814885812.5495049</t>
+          <t>813881121.3728814</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>67561114.0</t>
+          <t>31970280.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>57030358.8</v>
+        <v>55431253.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>58864658.8</t>
+          <t>55033166.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>105014037.38</v>
+        <v>104370124.22</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1834300</t>
+          <t>398087</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-8360252.191026547</t>
+          <t>-9043079.47071227</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-11490512.01097466</t>
+          <t>-12798629.50898375</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>67561114.0</t>
+          <t>31970280.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-35.33</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6679,22 +6679,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6744,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1402.498</t>
+          <t>1723.405</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-13.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-76.96</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6922,66 +6922,66 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>66.04</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>70.24</t>
+          <t>56.73</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>1.41</v>
+        <v>-2.17</v>
       </c>
       <c r="AI16" t="n">
-        <v>-5.63</v>
+        <v>-3.85</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-19.75</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.64</t>
+          <t>39.66</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>42</v>
+        <v>41.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>51.77</v>
+        <v>51.4</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>54.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>-3.92</v>
+        <v>-3.79</v>
       </c>
       <c r="AR16" t="n">
-        <v>-4.45</v>
+        <v>-4.32</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-144.66</t>
+          <t>-143.34</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>814885812.5495049</t>
+          <t>813881121.3728814</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>56866738.0</t>
+          <t>67561114.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>52170587</v>
+        <v>57030358.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>60387674.3</t>
+          <t>58864658.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>104657046.58</v>
+        <v>105014037.38</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-8217087</t>
+          <t>-1834300</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-7791114.041945071</t>
+          <t>-8360252.191026547</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-13024700.9419983</t>
+          <t>-11490512.01097466</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>56866738.0</t>
+          <t>67561114.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-35.33</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7101,22 +7101,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7166,22 +7166,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2004.052</t>
+          <t>1402.498</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-13.61</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-76.45</t>
+          <t>-76.96</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7344,66 +7344,66 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.04</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>70.24</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>4.16</v>
+        <v>1.41</v>
       </c>
       <c r="AI17" t="n">
-        <v>-7.83</v>
+        <v>-5.63</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>39.45999999999999</t>
+          <t>39.64</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>42.81</v>
+        <v>42</v>
       </c>
       <c r="AN17" t="n">
-        <v>52.12</v>
+        <v>51.77</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>-4.18</v>
+        <v>-3.92</v>
       </c>
       <c r="AR17" t="n">
-        <v>-4.58</v>
+        <v>-4.45</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-145.99</t>
+          <t>-144.66</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>814885812.5495049</t>
+          <t>813881121.3728814</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>81179444.0</t>
+          <t>56866738.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>52542179</v>
+        <v>52170587</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>70182172.1</t>
+          <t>60387674.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>104757662.2</v>
+        <v>104657046.58</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-17639993</t>
+          <t>-8217087</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6839552.787389938</t>
+          <t>-7791114.041945071</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-13605405.52410358</t>
+          <t>-13024700.9419983</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>81179444.0</t>
+          <t>56866738.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-31.50</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7523,22 +7523,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7588,22 +7588,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1008.964</t>
+          <t>2004.052</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7660,17 +7660,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-38.43</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-77.59</t>
+          <t>-76.45</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>12.16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7766,66 +7766,66 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>4.16</v>
       </c>
       <c r="AI18" t="n">
-        <v>-9.869999999999999</v>
+        <v>-7.83</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-16.88</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.45999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>43.62</v>
+        <v>42.81</v>
       </c>
       <c r="AN18" t="n">
-        <v>52.48</v>
+        <v>52.12</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>-4.53</v>
+        <v>-4.18</v>
       </c>
       <c r="AR18" t="n">
-        <v>-4.68</v>
+        <v>-4.58</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-147.00</t>
+          <t>-145.99</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>814885812.5495049</t>
+          <t>813881121.3728814</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>39578693.0</t>
+          <t>81179444.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>45879187.4</v>
+        <v>52542179</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>74516116.7</t>
+          <t>70182172.1</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>104984462.56</v>
+        <v>104757662.2</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-28636929</t>
+          <t>-17639993</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-5609397.744351093</t>
+          <t>-6839552.787389938</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-16554008.94410741</t>
+          <t>-13605405.52410358</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>39578693.0</t>
+          <t>81179444.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-34.83</t>
+          <t>-31.50</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -7945,22 +7945,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8015,17 +8015,17 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8047,7 +8047,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1019.0</t>
+          <t>1008.964</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-36.24</t>
+          <t>-38.43</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8188,12 +8188,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8203,51 +8203,51 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>-1.19</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AI19" t="n">
-        <v>-11.16</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.88</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>44.54</v>
+        <v>43.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>52.9</v>
+        <v>52.48</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>56.44</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>-4.72</v>
+        <v>-4.53</v>
       </c>
       <c r="AR19" t="n">
-        <v>-4.72</v>
+        <v>-4.68</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-147.37</t>
+          <t>-147.00</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>814885812.5495049</t>
+          <t>813881121.3728814</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>39965805.0</t>
+          <t>39578693.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>54635078.8</v>
+        <v>45879187.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>85690900.6</t>
+          <t>74516116.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>108163023.8</v>
+        <v>104984462.56</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-31055821</t>
+          <t>-28636929</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-3619468.435304489</t>
+          <t>-5609397.744351093</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-15717861.61753762</t>
+          <t>-16554008.94410741</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>39965805.0</t>
+          <t>39578693.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1116.892</t>
+          <t>1019.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-53.69</t>
+          <t>-36.24</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-77.82</t>
+          <t>-77.59</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8610,63 +8610,63 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>45.04</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>-1.88</v>
+        <v>-1.19</v>
       </c>
       <c r="AI20" t="n">
-        <v>-13.37</v>
+        <v>-11.16</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-14.54</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>45.52</v>
+        <v>44.54</v>
       </c>
       <c r="AN20" t="n">
-        <v>53.27</v>
+        <v>52.9</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>56.99</t>
+          <t>56.44</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>-4.89</v>
+        <v>-4.72</v>
       </c>
       <c r="AR20" t="n">
         <v>-4.72</v>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-147.36</t>
+          <t>-147.37</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>814885812.5495049</t>
+          <t>813881121.3728814</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>43262255.0</t>
+          <t>39965805.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>60698958.8</v>
+        <v>54635078.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>131072655.7</t>
+          <t>85690900.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>108812256.18</v>
+        <v>108163023.8</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-70373696</t>
+          <t>-31055821</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1419760.583989375</t>
+          <t>-3619468.435304489</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-14003489.52181157</t>
+          <t>-15717861.61753762</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>43262255.0</t>
+          <t>39965805.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-34.83</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8789,22 +8789,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8854,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1488.337</t>
+          <t>1116.892</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-48.94</t>
+          <t>-53.69</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.82</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,66 +9032,66 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>48.49</t>
+          <t>45.04</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>-0.03</v>
+        <v>-1.88</v>
       </c>
       <c r="AI21" t="n">
-        <v>-15.58</v>
+        <v>-13.37</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-13.13</t>
+          <t>-14.54</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>46.56</v>
+        <v>45.52</v>
       </c>
       <c r="AN21" t="n">
-        <v>53.6</v>
+        <v>53.27</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>56.99</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>-4.99</v>
+        <v>-4.89</v>
       </c>
       <c r="AR21" t="n">
-        <v>-4.67</v>
+        <v>-4.72</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-146.93</t>
+          <t>-147.36</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>814885812.5495049</t>
+          <t>813881121.3728814</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>58724698.0</t>
+          <t>43262255.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>68604761.59999999</v>
+        <v>60698958.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>134363485.4</t>
+          <t>131072655.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>108539531.38</v>
+        <v>108812256.18</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-65758723</t>
+          <t>-70373696</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>868190.1319782983</t>
+          <t>-1419760.583989375</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-11407452.9735668</t>
+          <t>-14003489.52181157</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>58724698.0</t>
+          <t>43262255.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9211,22 +9211,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1193.144</t>
+          <t>1488.337</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.10</t>
+          <t>-48.94</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9454,66 +9454,66 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>48.49</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>2.51</v>
+        <v>-0.03</v>
       </c>
       <c r="AI22" t="n">
-        <v>-17.28</v>
+        <v>-15.58</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-11.66</t>
+          <t>-13.13</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>39.41</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>47.64</v>
+        <v>46.56</v>
       </c>
       <c r="AN22" t="n">
-        <v>53.93</v>
+        <v>53.6</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>-5.11</v>
+        <v>-4.99</v>
       </c>
       <c r="AR22" t="n">
-        <v>-4.59</v>
+        <v>-4.67</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-146.12</t>
+          <t>-146.93</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>814885812.5495049</t>
+          <t>813881121.3728814</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>47864486.0</t>
+          <t>58724698.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>87822165.2</v>
+        <v>68604761.59999999</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>133257287.4</t>
+          <t>134363485.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>108220642.86</v>
+        <v>108539531.38</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-45435122</t>
+          <t>-65758723</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>3100125.242077407</t>
+          <t>868190.1319782983</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-8948110.61987549</t>
+          <t>-11407452.9735668</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>47864486.0</t>
+          <t>58724698.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9698,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2106.06</t>
+          <t>1193.144</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9770,17 +9770,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-27.07</t>
+          <t>-34.10</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-76.88</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9876,66 +9876,66 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>37.27</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>3.44</v>
+        <v>2.51</v>
       </c>
       <c r="AI23" t="n">
-        <v>-19.77</v>
+        <v>-17.28</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-10.35</t>
+          <t>-11.66</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>39.01000000000001</t>
+          <t>39.41</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>48.62</v>
+        <v>47.64</v>
       </c>
       <c r="AN23" t="n">
-        <v>54.24</v>
+        <v>53.93</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>58.61</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-18.89</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>-5.31</v>
+        <v>-5.11</v>
       </c>
       <c r="AR23" t="n">
-        <v>-4.46</v>
+        <v>-4.59</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-144.82</t>
+          <t>-146.12</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>814885812.5495049</t>
+          <t>813881121.3728814</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>103153046</v>
+        <v>87822165.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>141449078.375</t>
+          <t>133257287.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>108192095.52</v>
+        <v>108220642.86</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-38296032</t>
+          <t>-45435122</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>5290713.580614299</t>
+          <t>3100125.242077407</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-3951594.87817803</t>
+          <t>-8948110.61987549</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>83358150.0</t>
+          <t>47864486.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>325.394</t>
+          <t>1082.367</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-46.82</t>
+          <t>-48.67</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10277,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10298,66 +10298,66 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>-0.42</v>
+        <v>-2.98</v>
       </c>
       <c r="AI24" t="n">
-        <v>-2.23</v>
+        <v>-1.58</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-18.31</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>26.66</v>
+        <v>26.24</v>
       </c>
       <c r="AN24" t="n">
-        <v>32.29</v>
+        <v>32.11</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>33.29</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>-1.9</v>
+        <v>-1.87</v>
       </c>
       <c r="AR24" t="n">
-        <v>-2.2</v>
+        <v>-2.14</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-152.67</t>
+          <t>-151.07</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10376,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>231215984.904661</t>
+          <t>230947224.8039492</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>8485051.0</t>
+          <t>27110049.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>9251141.800000001</v>
+        <v>12498203</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>10503148.8</t>
+          <t>11587897.8</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>47419880.68</v>
+        <v>47316541.54</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-1252007</t>
+          <t>910305</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-5767345.171763203</t>
+          <t>-5533223.720448527</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-6086124.136914704</t>
+          <t>-4245555.738217814</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>8485051.0</t>
+          <t>27110049.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-31.26</t>
+          <t>-33.64</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
@@ -10477,22 +10477,22 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10517,12 +10517,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10542,22 +10542,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>385.635</t>
+          <t>325.394</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10614,17 +10614,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-18.75</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-46.72</t>
+          <t>-46.82</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10699,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10720,66 +10720,66 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>-0.27</v>
+        <v>-0.42</v>
       </c>
       <c r="AI25" t="n">
-        <v>-3.55</v>
+        <v>-2.23</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>27.03</v>
+        <v>26.66</v>
       </c>
       <c r="AN25" t="n">
-        <v>32.46</v>
+        <v>32.29</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="AR25" t="n">
-        <v>-2.28</v>
+        <v>-2.2</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-154.48</t>
+          <t>-152.67</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10798,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>231215984.904661</t>
+          <t>230947224.8039492</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>9968339.0</t>
+          <t>8485051.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>9257823.199999999</v>
+        <v>9251141.800000001</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>11393836.2</t>
+          <t>10503148.8</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>47719309.62</v>
+        <v>47419880.68</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-2136013</t>
+          <t>-1252007</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-5709385.359917476</t>
+          <t>-5767345.171763203</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-6502610.487306161</t>
+          <t>-6086124.136914704</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>9968339.0</t>
+          <t>8485051.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-31.13</t>
+          <t>-31.26</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -10964,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>300.074</t>
+          <t>385.635</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11036,17 +11036,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-20.04</t>
+          <t>-18.75</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11121,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11142,66 +11142,66 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>-0.34</v>
+        <v>-0.27</v>
       </c>
       <c r="AI26" t="n">
-        <v>-4.74</v>
+        <v>-3.55</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>27.39</v>
+        <v>27.03</v>
       </c>
       <c r="AN26" t="n">
-        <v>32.64</v>
+        <v>32.46</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-2.11</v>
+        <v>-2</v>
       </c>
       <c r="AR26" t="n">
-        <v>-2.35</v>
+        <v>-2.28</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-156.14</t>
+          <t>-154.48</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11220,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>231215984.904661</t>
+          <t>230947224.8039492</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>7827955.0</t>
+          <t>9968339.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>9442320.800000001</v>
+        <v>9257823.199999999</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>11809321.3</t>
+          <t>11393836.2</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>48370630.4</v>
+        <v>47719309.62</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-2367000</t>
+          <t>-2136013</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-5565162.609483169</t>
+          <t>-5709385.359917476</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-7024278.613318738</t>
+          <t>-6502610.487306161</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>7827955.0</t>
+          <t>9968339.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="BM26" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN26" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11386,17 +11386,17 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>345.581</t>
+          <t>300.074</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11458,17 +11458,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-20.52</t>
+          <t>-20.04</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-46.52</t>
+          <t>-46.72</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11543,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11564,66 +11564,66 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>0.31</v>
+        <v>-0.34</v>
       </c>
       <c r="AI27" t="n">
-        <v>-6.34</v>
+        <v>-4.74</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-15.31</t>
+          <t>-16.08</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>27.78</v>
+        <v>27.39</v>
       </c>
       <c r="AN27" t="n">
-        <v>32.8</v>
+        <v>32.64</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-2.21</v>
+        <v>-2.11</v>
       </c>
       <c r="AR27" t="n">
-        <v>-2.41</v>
+        <v>-2.35</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-157.58</t>
+          <t>-156.14</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11642,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>231215984.904661</t>
+          <t>230947224.8039492</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>9099621.0</t>
+          <t>7827955.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>10056805.4</v>
+        <v>9442320.800000001</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>12653110.1</t>
+          <t>11809321.3</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>48733537.5</v>
+        <v>48370630.4</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-2596304</t>
+          <t>-2367000</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-5299868.790603975</t>
+          <t>-5565162.609483169</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-7289324.842861038</t>
+          <t>-7024278.613318738</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>9099621.0</t>
+          <t>7827955.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-31.13</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="BM27" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN27" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -11808,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>412.175</t>
+          <t>345.581</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11880,17 +11880,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-20.52</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-46.21</t>
+          <t>-46.52</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11986,38 +11986,38 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="AI28" t="n">
-        <v>-7.67</v>
+        <v>-6.34</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-15.31</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -12026,26 +12026,26 @@
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>28.18</v>
+        <v>27.78</v>
       </c>
       <c r="AN28" t="n">
-        <v>32.97</v>
+        <v>32.8</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>-2.32</v>
+        <v>-2.21</v>
       </c>
       <c r="AR28" t="n">
-        <v>-2.46</v>
+        <v>-2.41</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-158.77</t>
+          <t>-157.58</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12064,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>231215984.904661</t>
+          <t>230947224.8039492</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>10874743.0</t>
+          <t>9099621.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>10677592.6</v>
+        <v>10056805.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>15303859.3</t>
+          <t>12653110.1</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>48839305.12</v>
+        <v>48733537.5</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-4626266</t>
+          <t>-2596304</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-4938149.508375417</t>
+          <t>-5299868.790603975</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-7543879.212104999</t>
+          <t>-7289324.842861038</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>10874743.0</t>
+          <t>9099621.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-30.46</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="BM28" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN28" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12230,22 +12230,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>324.726</t>
+          <t>412.175</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12302,17 +12302,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-35.94</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-46.72</t>
+          <t>-46.21</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12387,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12408,66 +12408,66 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>51.61</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>-0.34</v>
+        <v>0.88</v>
       </c>
       <c r="AI29" t="n">
-        <v>-8.76</v>
+        <v>-7.67</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>28.6</v>
+        <v>28.18</v>
       </c>
       <c r="AN29" t="n">
-        <v>33.14</v>
+        <v>32.97</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.51</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>-2.45</v>
+        <v>-2.32</v>
       </c>
       <c r="AR29" t="n">
-        <v>-2.49</v>
+        <v>-2.46</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-159.58</t>
+          <t>-158.77</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12486,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>231215984.904661</t>
+          <t>230947224.8039492</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>8518458.0</t>
+          <t>10874743.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>11755155.8</v>
+        <v>10677592.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>18350491.6</t>
+          <t>15303859.3</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>48982652.58</v>
+        <v>48839305.12</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-6595335</t>
+          <t>-4626266</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-4464380.471333675</t>
+          <t>-4938149.508375417</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-7828295.69630691</t>
+          <t>-7543879.212104999</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>8518458.0</t>
+          <t>10874743.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-31.13</t>
+          <t>-30.46</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="BM29" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN29" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12689,7 +12689,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>418.856</t>
+          <t>324.726</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12724,17 +12724,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-43.13</t>
+          <t>-35.94</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-46.52</t>
+          <t>-46.72</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12809,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12830,66 +12830,66 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>-0.72</v>
+        <v>-0.34</v>
       </c>
       <c r="AI30" t="n">
-        <v>-9.43</v>
+        <v>-8.76</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-12.88</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>26.29</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>29.03</v>
+        <v>28.6</v>
       </c>
       <c r="AN30" t="n">
-        <v>33.32</v>
+        <v>33.14</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>-2.54</v>
+        <v>-2.45</v>
       </c>
       <c r="AR30" t="n">
-        <v>-2.51</v>
+        <v>-2.49</v>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-159.87</t>
+          <t>-159.58</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12908,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>231215984.904661</t>
+          <t>230947224.8039492</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>10890827.0</t>
+          <t>8518458.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>13529849.2</v>
+        <v>11755155.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>23791154.3</t>
+          <t>18350491.6</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>49422294.62</v>
+        <v>48982652.58</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-10261305</t>
+          <t>-6595335</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-3852759.521338541</t>
+          <t>-4464380.471333675</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-7702563.863155823</t>
+          <t>-7828295.69630691</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>10890827.0</t>
+          <t>8518458.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-31.13</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="BM30" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN30" t="inlineStr">
@@ -13009,22 +13009,22 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13074,22 +13074,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
+          <t>26.2</t>
+        </is>
+      </c>
+      <c r="CE30" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="CF30" t="inlineStr">
+        <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="CE30" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="CF30" t="inlineStr">
-        <is>
-          <t>25.65</t>
-        </is>
-      </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13121,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>422.572</t>
+          <t>418.856</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13146,17 +13146,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-70.11</t>
+          <t>-43.13</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-47.44</t>
+          <t>-46.52</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13231,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13252,66 +13252,66 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>45.97</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>-2.47</v>
+        <v>-0.72</v>
       </c>
       <c r="AI31" t="n">
-        <v>-10.88</v>
+        <v>-9.43</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-12.88</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.29</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>29.51</v>
+        <v>29.03</v>
       </c>
       <c r="AN31" t="n">
-        <v>33.48</v>
+        <v>33.32</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>-2.64</v>
+        <v>-2.54</v>
       </c>
       <c r="AR31" t="n">
-        <v>-2.5</v>
+        <v>-2.51</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-159.66</t>
+          <t>-159.87</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13330,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>231215984.904661</t>
+          <t>230947224.8039492</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>10900378.0</t>
+          <t>10890827.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>14176321.8</v>
+        <v>13529849.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>47420905.2</t>
+          <t>23791154.3</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>49617005.26</v>
+        <v>49422294.62</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-33244583</t>
+          <t>-10261305</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-3152795.095553581</t>
+          <t>-3852759.521338541</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-7502037.784970127</t>
+          <t>-7702563.863155823</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>10900378.0</t>
+          <t>10890827.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-32.05</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="BM31" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN31" t="inlineStr">
@@ -13431,22 +13431,22 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13496,22 +13496,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>465.71</t>
+          <t>422.572</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13568,17 +13568,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-69.34</t>
+          <t>-70.11</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-46.52</t>
+          <t>-47.44</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13674,66 +13674,66 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>45.97</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>-0.61</v>
+        <v>-2.47</v>
       </c>
       <c r="AI32" t="n">
-        <v>-12.66</v>
+        <v>-10.88</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>30.07</v>
+        <v>29.51</v>
       </c>
       <c r="AN32" t="n">
-        <v>33.64</v>
+        <v>33.48</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>-2.68</v>
+        <v>-2.64</v>
       </c>
       <c r="AR32" t="n">
-        <v>-2.46</v>
+        <v>-2.5</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-158.82</t>
+          <t>-159.66</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13752,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>231215984.904661</t>
+          <t>230947224.8039492</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>12203557.0</t>
+          <t>10900378.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>15249414.8</v>
+        <v>14176321.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>49734645.5</t>
+          <t>47420905.2</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>49796767.5</v>
+        <v>49617005.26</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-34485230</t>
+          <t>-33244583</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-2362023.697477845</t>
+          <t>-3152795.095553581</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-6948665.359527342</t>
+          <t>-7502037.784970127</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>12203557.0</t>
+          <t>10900378.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-32.05</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="BM32" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN32" t="inlineStr">
@@ -13853,22 +13853,22 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -13893,12 +13893,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -13918,22 +13918,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>612.432</t>
+          <t>465.71</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-60.87</t>
+          <t>-69.34</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-45.49</t>
+          <t>-46.52</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14075,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14096,66 +14096,66 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>70.27</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>1.84</v>
+        <v>-0.61</v>
       </c>
       <c r="AI33" t="n">
-        <v>-14.68</v>
+        <v>-12.66</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>30.62</v>
+        <v>30.07</v>
       </c>
       <c r="AN33" t="n">
-        <v>33.79</v>
+        <v>33.64</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>-2.73</v>
+        <v>-2.68</v>
       </c>
       <c r="AR33" t="n">
-        <v>-2.41</v>
+        <v>-2.46</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-157.54</t>
+          <t>-158.82</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14174,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>231215984.904661</t>
+          <t>230947224.8039492</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>16262559.0</t>
+          <t>12203557.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>19930126</v>
+        <v>15249414.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>50938580.6</t>
+          <t>49734645.5</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>50167990.62</v>
+        <v>49796767.5</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-31008454</t>
+          <t>-34485230</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-1528088.849832482</t>
+          <t>-2362023.697477845</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-6049593.024625957</t>
+          <t>-6948665.359527342</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>16262559.0</t>
+          <t>12203557.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-29.54</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="BM33" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN33" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14285,12 +14285,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14315,12 +14315,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14340,22 +14340,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>649.691</t>
+          <t>612.432</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14412,17 +14412,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-52.69</t>
+          <t>-60.87</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-44.67</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14497,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14518,66 +14518,66 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>70.27</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>4.41</v>
+        <v>1.84</v>
       </c>
       <c r="AI34" t="n">
-        <v>-16.92</v>
+        <v>-14.68</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-9.4</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>31.12</v>
+        <v>30.62</v>
       </c>
       <c r="AN34" t="n">
-        <v>33.95</v>
+        <v>33.79</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>-2.81</v>
+        <v>-2.73</v>
       </c>
       <c r="AR34" t="n">
-        <v>-2.33</v>
+        <v>-2.41</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-155.61</t>
+          <t>-157.54</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14596,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>231215984.904661</t>
+          <t>230947224.8039492</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>24945827.4</v>
+        <v>19930126</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>52732533.125</t>
+          <t>50938580.6</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>50214218.22</v>
+        <v>50167990.62</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-27786705</t>
+          <t>-31008454</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-705997.1816882136</t>
+          <t>-1528088.849832482</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-4984040.152458765</t>
+          <t>-6049593.024625957</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>17391925.0</t>
+          <t>16262559.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-28.48</t>
+          <t>-29.54</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14707,12 +14707,12 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -14737,12 +14737,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">
